--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92516</v>
+        <v>135371874</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +982,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619035</v>
+        <v>618996</v>
       </c>
       <c r="R5" t="n">
-        <v>7347782</v>
+        <v>7347019</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1045,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1056,44 +1075,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122812</v>
+        <v>92516</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619270</v>
+        <v>619035</v>
       </c>
       <c r="R6" t="n">
-        <v>7348059</v>
+        <v>7347782</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1165,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92517</v>
+        <v>135371686</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,37 +1195,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R7" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1230,12 +1249,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,19 +1279,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85297</v>
+        <v>122812</v>
       </c>
       <c r="B8" t="n">
         <v>92183</v>
@@ -1293,17 +1322,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R8" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1327,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,44 +1376,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2042520</v>
+        <v>92517</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619830</v>
+        <v>619270</v>
       </c>
       <c r="R9" t="n">
-        <v>7347920</v>
+        <v>7348059</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1440,11 +1469,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1461,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>490387</v>
+        <v>85297</v>
       </c>
       <c r="B10" t="n">
-        <v>92083</v>
+        <v>92183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620514</v>
+        <v>619495</v>
       </c>
       <c r="R10" t="n">
-        <v>7347440</v>
+        <v>7347694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,48 +1582,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91817575</v>
+        <v>2042520</v>
       </c>
       <c r="B11" t="n">
-        <v>91831</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620488</v>
+        <v>619830</v>
       </c>
       <c r="R11" t="n">
-        <v>7347524</v>
+        <v>7347920</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1623,12 +1647,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1639,67 +1663,69 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55275159</v>
+        <v>490387</v>
       </c>
       <c r="B12" t="n">
-        <v>106229</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620460</v>
+        <v>620514</v>
       </c>
       <c r="R12" t="n">
-        <v>7347402</v>
+        <v>7347440</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1723,17 +1749,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1748,61 +1769,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>490385</v>
+        <v>91817575</v>
       </c>
       <c r="B13" t="n">
-        <v>92083</v>
+        <v>91831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621310</v>
+        <v>620488</v>
       </c>
       <c r="R13" t="n">
-        <v>7347725</v>
+        <v>7347524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1829,12 +1846,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,60 +1866,63 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>490388</v>
+        <v>55275159</v>
       </c>
       <c r="B14" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620881</v>
+        <v>620460</v>
       </c>
       <c r="R14" t="n">
-        <v>7347558</v>
+        <v>7347402</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1926,12 +1946,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,19 +1971,23 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>490389</v>
+        <v>490385</v>
       </c>
       <c r="B15" t="n">
         <v>92083</v>
@@ -1993,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621059</v>
+        <v>621310</v>
       </c>
       <c r="R15" t="n">
-        <v>7347676</v>
+        <v>7347725</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,6 +2081,200 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>490388</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620881</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135371874</v>
+        <v>135371985</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>78776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,43 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618996</v>
+        <v>618978</v>
       </c>
       <c r="R5" t="n">
-        <v>7347019</v>
+        <v>7346969</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1050,7 +1041,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1060,7 +1051,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92516</v>
+        <v>135371874</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1089,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619035</v>
+        <v>618996</v>
       </c>
       <c r="R6" t="n">
-        <v>7347782</v>
+        <v>7347019</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1152,12 +1152,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,19 +1182,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135371686</v>
+        <v>135372100</v>
       </c>
       <c r="B7" t="n">
         <v>79963</v>
@@ -1219,13 +1229,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619173</v>
+        <v>618980</v>
       </c>
       <c r="R7" t="n">
-        <v>7347221</v>
+        <v>7346943</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,7 +1264,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1264,7 +1274,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122812</v>
+        <v>92516</v>
       </c>
       <c r="B8" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619270</v>
+        <v>619035</v>
       </c>
       <c r="R8" t="n">
-        <v>7348059</v>
+        <v>7347782</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1388,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92517</v>
+        <v>135371686</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,37 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R9" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1453,12 +1463,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,19 +1493,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>85297</v>
+        <v>122812</v>
       </c>
       <c r="B10" t="n">
         <v>92183</v>
@@ -1516,17 +1536,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R10" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1550,12 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1570,44 +1590,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2042520</v>
+        <v>92517</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619830</v>
+        <v>619270</v>
       </c>
       <c r="R11" t="n">
-        <v>7347920</v>
+        <v>7348059</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1663,11 +1683,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1684,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>490387</v>
+        <v>85297</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620514</v>
+        <v>619495</v>
       </c>
       <c r="R12" t="n">
-        <v>7347440</v>
+        <v>7347694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,48 +1796,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91817575</v>
+        <v>2042520</v>
       </c>
       <c r="B13" t="n">
-        <v>91831</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620488</v>
+        <v>619830</v>
       </c>
       <c r="R13" t="n">
-        <v>7347524</v>
+        <v>7347920</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1846,12 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1862,67 +1877,69 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55275159</v>
+        <v>490387</v>
       </c>
       <c r="B14" t="n">
-        <v>106229</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620460</v>
+        <v>620514</v>
       </c>
       <c r="R14" t="n">
-        <v>7347402</v>
+        <v>7347440</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1946,17 +1963,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,61 +1983,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>490385</v>
+        <v>91817575</v>
       </c>
       <c r="B15" t="n">
-        <v>92083</v>
+        <v>91831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621310</v>
+        <v>620488</v>
       </c>
       <c r="R15" t="n">
-        <v>7347725</v>
+        <v>7347524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,12 +2060,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2072,60 +2080,63 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>490388</v>
+        <v>55275159</v>
       </c>
       <c r="B16" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620881</v>
+        <v>620460</v>
       </c>
       <c r="R16" t="n">
-        <v>7347558</v>
+        <v>7347402</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2149,12 +2160,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,19 +2185,23 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>490389</v>
+        <v>490385</v>
       </c>
       <c r="B17" t="n">
         <v>92083</v>
@@ -2216,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621059</v>
+        <v>621310</v>
       </c>
       <c r="R17" t="n">
-        <v>7347676</v>
+        <v>7347725</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,6 +2295,200 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>490388</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>620881</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>92516</v>
+        <v>135372226</v>
       </c>
       <c r="B8" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,37 +1312,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619035</v>
+        <v>618982</v>
       </c>
       <c r="R8" t="n">
-        <v>7347782</v>
+        <v>7346945</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1366,12 +1366,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,22 +1396,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135371686</v>
+        <v>92516</v>
       </c>
       <c r="B9" t="n">
-        <v>79963</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1419,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619173</v>
+        <v>619035</v>
       </c>
       <c r="R9" t="n">
-        <v>7347221</v>
+        <v>7347782</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,22 +1473,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,60 +1493,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122812</v>
+        <v>135371686</v>
       </c>
       <c r="B10" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R10" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1570,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,44 +1600,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>92517</v>
+        <v>122812</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>92183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,48 +1709,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85297</v>
+        <v>92517</v>
       </c>
       <c r="B12" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R12" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1784,60 +1794,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2042520</v>
+        <v>85297</v>
       </c>
       <c r="B13" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619830</v>
+        <v>619495</v>
       </c>
       <c r="R13" t="n">
-        <v>7347920</v>
+        <v>7347694</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1861,12 +1871,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1877,69 +1887,64 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>490387</v>
+        <v>2042520</v>
       </c>
       <c r="B14" t="n">
-        <v>92083</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620514</v>
+        <v>619830</v>
       </c>
       <c r="R14" t="n">
-        <v>7347440</v>
+        <v>7347920</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,12 +1968,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1979,61 +1984,66 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91817575</v>
+        <v>490387</v>
       </c>
       <c r="B15" t="n">
-        <v>91831</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620488</v>
+        <v>620514</v>
       </c>
       <c r="R15" t="n">
-        <v>7347524</v>
+        <v>7347440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,12 +2070,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2080,63 +2090,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55275159</v>
+        <v>91817575</v>
       </c>
       <c r="B16" t="n">
-        <v>106229</v>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620460</v>
+        <v>620488</v>
       </c>
       <c r="R16" t="n">
-        <v>7347402</v>
+        <v>7347524</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2160,17 +2167,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,64 +2187,63 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>490385</v>
+        <v>55275159</v>
       </c>
       <c r="B17" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621310</v>
+        <v>620460</v>
       </c>
       <c r="R17" t="n">
-        <v>7347725</v>
+        <v>7347402</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2266,12 +2267,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,19 +2292,23 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>490388</v>
+        <v>490385</v>
       </c>
       <c r="B18" t="n">
         <v>92083</v>
@@ -2333,10 +2343,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620881</v>
+        <v>621310</v>
       </c>
       <c r="R18" t="n">
-        <v>7347558</v>
+        <v>7347725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,7 +2405,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>490389</v>
+        <v>490388</v>
       </c>
       <c r="B19" t="n">
         <v>92083</v>
@@ -2430,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621059</v>
+        <v>620881</v>
       </c>
       <c r="R19" t="n">
-        <v>7347676</v>
+        <v>7347558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,6 +2499,103 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135371985</v>
+        <v>135372813</v>
       </c>
       <c r="B5" t="n">
-        <v>78776</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618978</v>
+        <v>618915</v>
       </c>
       <c r="R5" t="n">
-        <v>7346969</v>
+        <v>7346854</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135371874</v>
+        <v>135372935</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,43 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618996</v>
+        <v>618926</v>
       </c>
       <c r="R6" t="n">
-        <v>7347019</v>
+        <v>7346758</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1157,7 +1148,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1167,7 +1158,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135372100</v>
+        <v>135371985</v>
       </c>
       <c r="B7" t="n">
-        <v>79963</v>
+        <v>78776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618980</v>
+        <v>618978</v>
       </c>
       <c r="R7" t="n">
-        <v>7346943</v>
+        <v>7346969</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,7 +1255,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1274,7 +1265,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135372226</v>
+        <v>135372847</v>
       </c>
       <c r="B8" t="n">
-        <v>79963</v>
+        <v>78776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618982</v>
+        <v>618881</v>
       </c>
       <c r="R8" t="n">
-        <v>7346945</v>
+        <v>7346818</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1381,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92516</v>
+        <v>135371874</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,37 +1410,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619035</v>
+        <v>618996</v>
       </c>
       <c r="R9" t="n">
-        <v>7347782</v>
+        <v>7347019</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,12 +1473,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,19 +1503,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135371686</v>
+        <v>135372100</v>
       </c>
       <c r="B10" t="n">
         <v>79963</v>
@@ -1540,13 +1550,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619173</v>
+        <v>618980</v>
       </c>
       <c r="R10" t="n">
-        <v>7347221</v>
+        <v>7346943</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,7 +1585,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1585,7 +1595,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,48 +1622,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122812</v>
+        <v>135372226</v>
       </c>
       <c r="B11" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619270</v>
+        <v>618982</v>
       </c>
       <c r="R11" t="n">
-        <v>7348059</v>
+        <v>7346945</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1677,12 +1687,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,19 +1717,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92517</v>
+        <v>92516</v>
       </c>
       <c r="B12" t="n">
         <v>78993</v>
@@ -1744,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619270</v>
+        <v>619035</v>
       </c>
       <c r="R12" t="n">
-        <v>7348059</v>
+        <v>7347782</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -1806,48 +1826,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>85297</v>
+        <v>135371686</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619495</v>
+        <v>619173</v>
       </c>
       <c r="R13" t="n">
-        <v>7347694</v>
+        <v>7347221</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1871,12 +1891,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,44 +1921,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2042520</v>
+        <v>122812</v>
       </c>
       <c r="B14" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1938,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619830</v>
+        <v>619270</v>
       </c>
       <c r="R14" t="n">
-        <v>7347920</v>
+        <v>7348059</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -1984,11 +2014,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2005,48 +2030,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>490387</v>
+        <v>92517</v>
       </c>
       <c r="B15" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620514</v>
+        <v>619270</v>
       </c>
       <c r="R15" t="n">
-        <v>7347440</v>
+        <v>7348059</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2070,12 +2095,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2090,57 +2115,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91817575</v>
+        <v>85297</v>
       </c>
       <c r="B16" t="n">
-        <v>91831</v>
+        <v>92183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>65</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620488</v>
+        <v>619495</v>
       </c>
       <c r="R16" t="n">
-        <v>7347524</v>
+        <v>7347694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2167,12 +2192,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,22 +2212,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55275159</v>
+        <v>2042520</v>
       </c>
       <c r="B17" t="n">
-        <v>106229</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,40 +2235,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620460</v>
+        <v>619830</v>
       </c>
       <c r="R17" t="n">
-        <v>7347402</v>
+        <v>7347920</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2267,17 +2289,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2288,27 +2305,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>490385</v>
+        <v>490387</v>
       </c>
       <c r="B18" t="n">
         <v>92083</v>
@@ -2343,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621310</v>
+        <v>620514</v>
       </c>
       <c r="R18" t="n">
-        <v>7347725</v>
+        <v>7347440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,45 +2423,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>490388</v>
+        <v>91817575</v>
       </c>
       <c r="B19" t="n">
-        <v>92083</v>
+        <v>91831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620881</v>
+        <v>620488</v>
       </c>
       <c r="R19" t="n">
-        <v>7347558</v>
+        <v>7347524</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2470,12 +2488,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2490,60 +2508,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>490389</v>
+        <v>55275159</v>
       </c>
       <c r="B20" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621059</v>
+        <v>620460</v>
       </c>
       <c r="R20" t="n">
-        <v>7347676</v>
+        <v>7347402</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2567,12 +2588,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,15 +2613,310 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>490385</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>621310</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7347725</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>490388</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620881</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135371985</v>
+        <v>135372979</v>
       </c>
       <c r="B7" t="n">
-        <v>78776</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618978</v>
+        <v>618964</v>
       </c>
       <c r="R7" t="n">
-        <v>7346969</v>
+        <v>7346744</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135372847</v>
+        <v>135371985</v>
       </c>
       <c r="B8" t="n">
         <v>78776</v>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618881</v>
+        <v>618978</v>
       </c>
       <c r="R8" t="n">
-        <v>7346818</v>
+        <v>7346969</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135371874</v>
+        <v>135372847</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>78776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,46 +1410,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618996</v>
+        <v>618881</v>
       </c>
       <c r="R9" t="n">
-        <v>7347019</v>
+        <v>7346818</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1488,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135372100</v>
+        <v>135371874</v>
       </c>
       <c r="B10" t="n">
-        <v>79963</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,37 +1517,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618980</v>
+        <v>618996</v>
       </c>
       <c r="R10" t="n">
-        <v>7346943</v>
+        <v>7347019</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135372226</v>
+        <v>135373243</v>
       </c>
       <c r="B11" t="n">
-        <v>79963</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,37 +1633,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618982</v>
+        <v>618966</v>
       </c>
       <c r="R11" t="n">
-        <v>7346945</v>
+        <v>7346745</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,7 +1706,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1702,7 +1716,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,48 +1743,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92516</v>
+        <v>135373563</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>79050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228654</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grå renlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cladonia rangiferina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) F.H.Wigg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619035</v>
+        <v>618906</v>
       </c>
       <c r="R12" t="n">
-        <v>7347782</v>
+        <v>7346564</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,12 +1808,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,19 +1838,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135371686</v>
+        <v>135372100</v>
       </c>
       <c r="B13" t="n">
         <v>79963</v>
@@ -1861,13 +1885,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619173</v>
+        <v>618980</v>
       </c>
       <c r="R13" t="n">
-        <v>7347221</v>
+        <v>7346943</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1896,7 +1920,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1906,7 +1930,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,48 +1957,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122812</v>
+        <v>135372226</v>
       </c>
       <c r="B14" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619270</v>
+        <v>618982</v>
       </c>
       <c r="R14" t="n">
-        <v>7348059</v>
+        <v>7346945</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,12 +2022,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2018,19 +2052,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>92517</v>
+        <v>92516</v>
       </c>
       <c r="B15" t="n">
         <v>78993</v>
@@ -2065,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619270</v>
+        <v>619035</v>
       </c>
       <c r="R15" t="n">
-        <v>7348059</v>
+        <v>7347782</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2127,48 +2161,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>85297</v>
+        <v>135371686</v>
       </c>
       <c r="B16" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619495</v>
+        <v>619173</v>
       </c>
       <c r="R16" t="n">
-        <v>7347694</v>
+        <v>7347221</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2192,12 +2226,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,44 +2256,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2042520</v>
+        <v>122812</v>
       </c>
       <c r="B17" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619830</v>
+        <v>619270</v>
       </c>
       <c r="R17" t="n">
-        <v>7347920</v>
+        <v>7348059</v>
       </c>
       <c r="S17" t="n">
         <v>100</v>
@@ -2305,11 +2349,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2326,48 +2365,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>490387</v>
+        <v>92517</v>
       </c>
       <c r="B18" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620514</v>
+        <v>619270</v>
       </c>
       <c r="R18" t="n">
-        <v>7347440</v>
+        <v>7348059</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,12 +2430,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2411,57 +2450,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>91817575</v>
+        <v>85297</v>
       </c>
       <c r="B19" t="n">
-        <v>91831</v>
+        <v>92183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620488</v>
+        <v>619495</v>
       </c>
       <c r="R19" t="n">
-        <v>7347524</v>
+        <v>7347694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,12 +2527,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,22 +2547,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55275159</v>
+        <v>2042520</v>
       </c>
       <c r="B20" t="n">
-        <v>106229</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,40 +2570,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620460</v>
+        <v>619830</v>
       </c>
       <c r="R20" t="n">
-        <v>7347402</v>
+        <v>7347920</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2588,17 +2624,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,27 +2640,28 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>490385</v>
+        <v>490387</v>
       </c>
       <c r="B21" t="n">
         <v>92083</v>
@@ -2664,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621310</v>
+        <v>620514</v>
       </c>
       <c r="R21" t="n">
-        <v>7347725</v>
+        <v>7347440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,45 +2758,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>490388</v>
+        <v>91817575</v>
       </c>
       <c r="B22" t="n">
-        <v>92083</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620881</v>
+        <v>620488</v>
       </c>
       <c r="R22" t="n">
-        <v>7347558</v>
+        <v>7347524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,12 +2823,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,60 +2843,63 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>490389</v>
+        <v>55275159</v>
       </c>
       <c r="B23" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621059</v>
+        <v>620460</v>
       </c>
       <c r="R23" t="n">
-        <v>7347676</v>
+        <v>7347402</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2888,12 +2923,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,15 +2948,310 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>490385</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>621310</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7347725</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>490388</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>620881</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>92516</v>
+        <v>135373694</v>
       </c>
       <c r="B15" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,37 +2075,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619035</v>
+        <v>618945</v>
       </c>
       <c r="R15" t="n">
-        <v>7347782</v>
+        <v>7346535</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,12 +2129,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2149,22 +2159,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135371686</v>
+        <v>92516</v>
       </c>
       <c r="B16" t="n">
-        <v>79963</v>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,37 +2182,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619173</v>
+        <v>619035</v>
       </c>
       <c r="R16" t="n">
-        <v>7347221</v>
+        <v>7347782</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2226,22 +2236,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,60 +2256,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122812</v>
+        <v>135371686</v>
       </c>
       <c r="B17" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R17" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2333,12 +2333,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,44 +2363,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>92517</v>
+        <v>122812</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>92183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,48 +2472,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85297</v>
+        <v>92517</v>
       </c>
       <c r="B19" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R19" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2527,12 +2537,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,60 +2557,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2042520</v>
+        <v>85297</v>
       </c>
       <c r="B20" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619830</v>
+        <v>619495</v>
       </c>
       <c r="R20" t="n">
-        <v>7347920</v>
+        <v>7347694</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2624,12 +2634,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,69 +2650,64 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>490387</v>
+        <v>2042520</v>
       </c>
       <c r="B21" t="n">
-        <v>92083</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620514</v>
+        <v>619830</v>
       </c>
       <c r="R21" t="n">
-        <v>7347440</v>
+        <v>7347920</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2726,12 +2731,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,61 +2747,66 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>91817575</v>
+        <v>490387</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>92083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620488</v>
+        <v>620514</v>
       </c>
       <c r="R22" t="n">
-        <v>7347524</v>
+        <v>7347440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,12 +2833,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,63 +2853,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55275159</v>
+        <v>91817575</v>
       </c>
       <c r="B23" t="n">
-        <v>106229</v>
+        <v>91831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620460</v>
+        <v>620488</v>
       </c>
       <c r="R23" t="n">
-        <v>7347402</v>
+        <v>7347524</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2923,17 +2930,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,64 +2950,63 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>490385</v>
+        <v>55275159</v>
       </c>
       <c r="B24" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621310</v>
+        <v>620460</v>
       </c>
       <c r="R24" t="n">
-        <v>7347725</v>
+        <v>7347402</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3029,12 +3030,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,19 +3055,23 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>490388</v>
+        <v>490385</v>
       </c>
       <c r="B25" t="n">
         <v>92083</v>
@@ -3096,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620881</v>
+        <v>621310</v>
       </c>
       <c r="R25" t="n">
-        <v>7347558</v>
+        <v>7347725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,7 +3168,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>490389</v>
+        <v>490388</v>
       </c>
       <c r="B26" t="n">
         <v>92083</v>
@@ -3193,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621059</v>
+        <v>620881</v>
       </c>
       <c r="R26" t="n">
-        <v>7347676</v>
+        <v>7347558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3252,6 +3262,103 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92515</v>
+        <v>135374074</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619250</v>
+        <v>618951</v>
       </c>
       <c r="R3" t="n">
-        <v>7346995</v>
+        <v>7346334</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>309457</v>
+        <v>92515</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135372813</v>
+        <v>309457</v>
       </c>
       <c r="B5" t="n">
-        <v>93271</v>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618915</v>
+        <v>619250</v>
       </c>
       <c r="R5" t="n">
-        <v>7346854</v>
+        <v>7346995</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,23 +1057,28 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135372935</v>
+        <v>135372813</v>
       </c>
       <c r="B6" t="n">
         <v>93271</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618926</v>
+        <v>618915</v>
       </c>
       <c r="R6" t="n">
-        <v>7346758</v>
+        <v>7346854</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135372979</v>
+        <v>135372935</v>
       </c>
       <c r="B7" t="n">
         <v>93271</v>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618964</v>
+        <v>618926</v>
       </c>
       <c r="R7" t="n">
-        <v>7346744</v>
+        <v>7346758</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135371985</v>
+        <v>135372979</v>
       </c>
       <c r="B8" t="n">
-        <v>78776</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618978</v>
+        <v>618964</v>
       </c>
       <c r="R8" t="n">
-        <v>7346969</v>
+        <v>7346744</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135372847</v>
+        <v>135371985</v>
       </c>
       <c r="B9" t="n">
         <v>78776</v>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618881</v>
+        <v>618978</v>
       </c>
       <c r="R9" t="n">
-        <v>7346818</v>
+        <v>7346969</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135371874</v>
+        <v>135372847</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>78776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,46 +1517,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618996</v>
+        <v>618881</v>
       </c>
       <c r="R10" t="n">
-        <v>7347019</v>
+        <v>7346818</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1585,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1595,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135373243</v>
+        <v>135371874</v>
       </c>
       <c r="B11" t="n">
         <v>58136</v>
@@ -1655,14 +1646,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1671,13 +1657,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618966</v>
+        <v>618996</v>
       </c>
       <c r="R11" t="n">
-        <v>7346745</v>
+        <v>7347019</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,7 +1692,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1716,7 +1702,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,48 +1729,62 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135373563</v>
+        <v>135373243</v>
       </c>
       <c r="B12" t="n">
-        <v>79050</v>
+        <v>58136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228654</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618906</v>
+        <v>618966</v>
       </c>
       <c r="R12" t="n">
-        <v>7346564</v>
+        <v>7346745</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,32 +1850,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135372100</v>
+        <v>135373563</v>
       </c>
       <c r="B13" t="n">
-        <v>79963</v>
+        <v>79050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>228654</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grå renlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia rangiferina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) F.H.Wigg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618980</v>
+        <v>618906</v>
       </c>
       <c r="R13" t="n">
-        <v>7346943</v>
+        <v>7346564</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,7 +1957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135372226</v>
+        <v>135372100</v>
       </c>
       <c r="B14" t="n">
         <v>79963</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618982</v>
+        <v>618980</v>
       </c>
       <c r="R14" t="n">
-        <v>7346945</v>
+        <v>7346943</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135373694</v>
+        <v>135372226</v>
       </c>
       <c r="B15" t="n">
         <v>79963</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618945</v>
+        <v>618982</v>
       </c>
       <c r="R15" t="n">
-        <v>7346535</v>
+        <v>7346945</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>92516</v>
+        <v>135373694</v>
       </c>
       <c r="B16" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,37 +2182,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619035</v>
+        <v>618945</v>
       </c>
       <c r="R16" t="n">
-        <v>7347782</v>
+        <v>7346535</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,12 +2236,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,22 +2266,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135371686</v>
+        <v>92516</v>
       </c>
       <c r="B17" t="n">
-        <v>79963</v>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,37 +2289,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619173</v>
+        <v>619035</v>
       </c>
       <c r="R17" t="n">
-        <v>7347221</v>
+        <v>7347782</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2333,22 +2343,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,60 +2363,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122812</v>
+        <v>135371686</v>
       </c>
       <c r="B18" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R18" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,12 +2440,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2460,44 +2470,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92517</v>
+        <v>122812</v>
       </c>
       <c r="B19" t="n">
-        <v>78993</v>
+        <v>92183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,48 +2579,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85297</v>
+        <v>92517</v>
       </c>
       <c r="B20" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R20" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2634,12 +2644,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,60 +2664,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2042520</v>
+        <v>85297</v>
       </c>
       <c r="B21" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619830</v>
+        <v>619495</v>
       </c>
       <c r="R21" t="n">
-        <v>7347920</v>
+        <v>7347694</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2731,12 +2741,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,69 +2757,64 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>490387</v>
+        <v>2042520</v>
       </c>
       <c r="B22" t="n">
-        <v>92083</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620514</v>
+        <v>619830</v>
       </c>
       <c r="R22" t="n">
-        <v>7347440</v>
+        <v>7347920</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,12 +2838,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,61 +2854,66 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>91817575</v>
+        <v>490387</v>
       </c>
       <c r="B23" t="n">
-        <v>91831</v>
+        <v>92083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620488</v>
+        <v>620514</v>
       </c>
       <c r="R23" t="n">
-        <v>7347524</v>
+        <v>7347440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2940,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2950,63 +2960,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55275159</v>
+        <v>91817575</v>
       </c>
       <c r="B24" t="n">
-        <v>106229</v>
+        <v>91831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>3242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620460</v>
+        <v>620488</v>
       </c>
       <c r="R24" t="n">
-        <v>7347402</v>
+        <v>7347524</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3030,17 +3037,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,64 +3057,63 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>490385</v>
+        <v>55275159</v>
       </c>
       <c r="B25" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621310</v>
+        <v>620460</v>
       </c>
       <c r="R25" t="n">
-        <v>7347725</v>
+        <v>7347402</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3136,12 +3137,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,19 +3162,23 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>490388</v>
+        <v>490385</v>
       </c>
       <c r="B26" t="n">
         <v>92083</v>
@@ -3203,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620881</v>
+        <v>621310</v>
       </c>
       <c r="R26" t="n">
-        <v>7347558</v>
+        <v>7347725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>490389</v>
+        <v>490388</v>
       </c>
       <c r="B27" t="n">
         <v>92083</v>
@@ -3300,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621059</v>
+        <v>620881</v>
       </c>
       <c r="R27" t="n">
-        <v>7347676</v>
+        <v>7347558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3359,6 +3369,103 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,48 +1850,62 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135373563</v>
+        <v>135376029</v>
       </c>
       <c r="B13" t="n">
-        <v>79050</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228654</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Råssneviken, Råssneviken, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618906</v>
+        <v>619367</v>
       </c>
       <c r="R13" t="n">
-        <v>7346564</v>
+        <v>7347134</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1920,7 +1934,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1930,7 +1944,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,32 +1971,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135372100</v>
+        <v>135373563</v>
       </c>
       <c r="B14" t="n">
-        <v>79963</v>
+        <v>79050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>228654</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grå renlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia rangiferina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) F.H.Wigg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,13 +2006,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618980</v>
+        <v>618906</v>
       </c>
       <c r="R14" t="n">
-        <v>7346943</v>
+        <v>7346564</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,7 +2041,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2037,7 +2051,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,7 +2078,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135372226</v>
+        <v>135372100</v>
       </c>
       <c r="B15" t="n">
         <v>79963</v>
@@ -2099,13 +2113,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618982</v>
+        <v>618980</v>
       </c>
       <c r="R15" t="n">
-        <v>7346945</v>
+        <v>7346943</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2134,7 +2148,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2144,7 +2158,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,7 +2185,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135373694</v>
+        <v>135372226</v>
       </c>
       <c r="B16" t="n">
         <v>79963</v>
@@ -2206,13 +2220,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618945</v>
+        <v>618982</v>
       </c>
       <c r="R16" t="n">
-        <v>7346535</v>
+        <v>7346945</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2255,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2265,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92516</v>
+        <v>135373694</v>
       </c>
       <c r="B17" t="n">
-        <v>78993</v>
+        <v>79963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,37 +2303,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619035</v>
+        <v>618945</v>
       </c>
       <c r="R17" t="n">
-        <v>7347782</v>
+        <v>7346535</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,12 +2357,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,22 +2387,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135371686</v>
+        <v>92516</v>
       </c>
       <c r="B18" t="n">
-        <v>79963</v>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2386,37 +2410,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Råssnesudden, Råssnesudden, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619173</v>
+        <v>619035</v>
       </c>
       <c r="R18" t="n">
-        <v>7347221</v>
+        <v>7347782</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2440,22 +2464,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2470,60 +2484,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122812</v>
+        <v>135371686</v>
       </c>
       <c r="B19" t="n">
-        <v>92183</v>
+        <v>79963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Råssnesudden, Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619270</v>
+        <v>619173</v>
       </c>
       <c r="R19" t="n">
-        <v>7348059</v>
+        <v>7347221</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,12 +2561,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,44 +2591,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>92517</v>
+        <v>122812</v>
       </c>
       <c r="B20" t="n">
-        <v>78993</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,48 +2700,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85297</v>
+        <v>92517</v>
       </c>
       <c r="B21" t="n">
-        <v>92183</v>
+        <v>78993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619495</v>
+        <v>619270</v>
       </c>
       <c r="R21" t="n">
-        <v>7347694</v>
+        <v>7348059</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2741,12 +2765,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2761,60 +2785,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2042520</v>
+        <v>85297</v>
       </c>
       <c r="B22" t="n">
-        <v>80461</v>
+        <v>92183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619830</v>
+        <v>619495</v>
       </c>
       <c r="R22" t="n">
-        <v>7347920</v>
+        <v>7347694</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2838,12 +2862,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2003-09-03</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,69 +2878,64 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>490387</v>
+        <v>2042520</v>
       </c>
       <c r="B23" t="n">
-        <v>92083</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Iksjak 15 km SV om Lövnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620514</v>
+        <v>619830</v>
       </c>
       <c r="R23" t="n">
-        <v>7347440</v>
+        <v>7347920</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2940,12 +2959,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2003-09-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,61 +2975,66 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>91817575</v>
+        <v>490387</v>
       </c>
       <c r="B24" t="n">
-        <v>91831</v>
+        <v>92083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Iksjak-Råssnesudden, Pi lm</t>
+          <t>Alep och Lulep Iksják, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620488</v>
+        <v>620514</v>
       </c>
       <c r="R24" t="n">
-        <v>7347524</v>
+        <v>7347440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,12 +3061,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3057,63 +3081,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55275159</v>
+        <v>91817575</v>
       </c>
       <c r="B25" t="n">
-        <v>106229</v>
+        <v>91831</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>3242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
+          <t>Iksjak-Råssnesudden, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620460</v>
+        <v>620488</v>
       </c>
       <c r="R25" t="n">
-        <v>7347402</v>
+        <v>7347524</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3137,17 +3158,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>30-tal</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3162,64 +3178,63 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>490385</v>
+        <v>55275159</v>
       </c>
       <c r="B26" t="n">
-        <v>92083</v>
+        <v>106229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Ruossnebäcken mellan Hornavan och Pleutajokkvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621310</v>
+        <v>620460</v>
       </c>
       <c r="R26" t="n">
-        <v>7347725</v>
+        <v>7347402</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3243,12 +3258,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2015-07-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>30-tal</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,19 +3283,23 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>490388</v>
+        <v>490385</v>
       </c>
       <c r="B27" t="n">
         <v>92083</v>
@@ -3310,10 +3334,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620881</v>
+        <v>621310</v>
       </c>
       <c r="R27" t="n">
-        <v>7347558</v>
+        <v>7347725</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,7 +3396,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>490389</v>
+        <v>490388</v>
       </c>
       <c r="B28" t="n">
         <v>92083</v>
@@ -3407,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621059</v>
+        <v>620881</v>
       </c>
       <c r="R28" t="n">
-        <v>7347676</v>
+        <v>7347558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,6 +3490,103 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3299,48 +3299,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>490385</v>
+        <v>135377105</v>
       </c>
       <c r="B27" t="n">
-        <v>92083</v>
+        <v>86538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>1081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gullmurkling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Neolecta vitellina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Bres.) Korf &amp; J.K.Rogers</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Råssnenjárrga, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621310</v>
+        <v>621041</v>
       </c>
       <c r="R27" t="n">
-        <v>7347725</v>
+        <v>7346803</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3364,12 +3364,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3384,60 +3394,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>490388</v>
+        <v>135377107</v>
       </c>
       <c r="B28" t="n">
-        <v>92083</v>
+        <v>87625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>3639</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Råssnenjárrga, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620881</v>
+        <v>620900</v>
       </c>
       <c r="R28" t="n">
-        <v>7347558</v>
+        <v>7346871</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3461,12 +3475,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3481,22 +3505,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>490389</v>
+        <v>135377083</v>
       </c>
       <c r="B29" t="n">
-        <v>92083</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,37 +3532,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Alep och Lulep Iksják, Pi lm</t>
+          <t>Råssnenjárrga, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621059</v>
+        <v>621506</v>
       </c>
       <c r="R29" t="n">
-        <v>7347676</v>
+        <v>7347011</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3558,12 +3586,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,15 +3616,5438 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135377084</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>621468</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7346973</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135377086</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>621482</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7346942</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135377102</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>621120</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7346725</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135377109</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>621097</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7346922</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135377087</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>621484</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7346943</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135377091</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>621296</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7346748</v>
+      </c>
+      <c r="S35" t="n">
+        <v>28</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135377085</v>
+      </c>
+      <c r="B36" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>621468</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7346964</v>
+      </c>
+      <c r="S36" t="n">
+        <v>56</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135377110</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>621167</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7346921</v>
+      </c>
+      <c r="S37" t="n">
+        <v>16</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135377111</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>621171</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7346923</v>
+      </c>
+      <c r="S38" t="n">
+        <v>23</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135377112</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>621208</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7346936</v>
+      </c>
+      <c r="S39" t="n">
+        <v>36</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135377114</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>621219</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7346965</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135377092</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>621292</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7346711</v>
+      </c>
+      <c r="S41" t="n">
+        <v>16</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135377093</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>621278</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7346702</v>
+      </c>
+      <c r="S42" t="n">
+        <v>14</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135377094</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>621290</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7346699</v>
+      </c>
+      <c r="S43" t="n">
+        <v>26</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135377095</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>621280</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7346686</v>
+      </c>
+      <c r="S44" t="n">
+        <v>36</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135377097</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>621248</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7346678</v>
+      </c>
+      <c r="S45" t="n">
+        <v>21</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135377098</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>621228</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7346707</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135377100</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>621205</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7346713</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135377108</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>620889</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7346894</v>
+      </c>
+      <c r="S48" t="n">
+        <v>14</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135377089</v>
+      </c>
+      <c r="B49" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>621452</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7346931</v>
+      </c>
+      <c r="S49" t="n">
+        <v>19</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135377096</v>
+      </c>
+      <c r="B50" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>621280</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7346686</v>
+      </c>
+      <c r="S50" t="n">
+        <v>18</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135377104</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>621071</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7346733</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135377090</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>621439</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7346903</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>490385</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>621310</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7347725</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>Mats Williamson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>490388</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>620881</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>490389</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Alep och Lulep Iksják, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>621059</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7347676</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135377136</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>621307</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7347651</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135377125</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>621281</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7347411</v>
+      </c>
+      <c r="S57" t="n">
+        <v>22</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135377124</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>621317</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7347405</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135377143</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>621239</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7347773</v>
+      </c>
+      <c r="S59" t="n">
+        <v>12</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135377140</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>621302</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7347717</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135377126</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>621266</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7347461</v>
+      </c>
+      <c r="S61" t="n">
+        <v>21</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135377118</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>621180</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7347252</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135377119</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>621179</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7347260</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135377121</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>621198</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7347313</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135377130</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>621325</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7347595</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135377137</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>621288</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7347662</v>
+      </c>
+      <c r="S66" t="n">
+        <v>18</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135377138</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>621311</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7347663</v>
+      </c>
+      <c r="S67" t="n">
+        <v>19</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135377139</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>621318</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7347705</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135377144</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>621227</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7347778</v>
+      </c>
+      <c r="S69" t="n">
+        <v>12</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135377145</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>621293</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7347923</v>
+      </c>
+      <c r="S70" t="n">
+        <v>21</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135377080</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>621514</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7347103</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135377081</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>621513</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7347051</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135377079</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>621511</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7347160</v>
+      </c>
+      <c r="S73" t="n">
+        <v>30</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135377070</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80489</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>621605</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7347494</v>
+      </c>
+      <c r="S74" t="n">
+        <v>14</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135377077</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93296</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>621526</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7347311</v>
+      </c>
+      <c r="S75" t="n">
+        <v>18</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135377074</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>621619</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7347445</v>
+      </c>
+      <c r="S76" t="n">
+        <v>11</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135377071</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>621610</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7347491</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135377076</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Råssnenjárrga, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>621596</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7347368</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -28346,6 +28346,9 @@
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
           <t>Råssnenjárrga, Pi lm</t>
@@ -28400,17 +28403,13 @@
           <t>13:27</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Kollekt 2, med ngn konstig knöl?</t>
-        </is>
-      </c>
       <c r="AD251" t="b">
         <v>0</v>
       </c>
       <c r="AE251" t="b">
         <v>0</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -38554,7 +38554,7 @@
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Sofia Fransén, Martin Axegård</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -38554,7 +38554,7 @@
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Sofia Fransén, Martin Axegård</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY537"/>
+  <dimension ref="A1:AZ537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380374</t>
         </is>
       </c>
     </row>
@@ -888,6 +898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135387752</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384630</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384624</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380660</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380363</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1998,6 +2058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2109,6 +2174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380368</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380375</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2331,6 +2406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380664</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2442,6 +2522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384623</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2553,6 +2638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380657</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2664,6 +2754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380658</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2761,6 +2856,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2552882</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380371</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2983,6 +3088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380661</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3094,6 +3204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380663</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3205,6 +3320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3316,6 +3436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380369</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3538,6 +3668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383022</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3654,6 +3789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380665</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3775,6 +3915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384628</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3896,6 +4041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384629</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4012,6 +4162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4131,6 +4286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384619</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4250,6 +4410,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384626</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4361,6 +4526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380370</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4472,6 +4642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380373</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4583,6 +4758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380659</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4694,6 +4874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383021</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4805,6 +4990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383024</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4916,6 +5106,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5027,6 +5222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384632</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5138,6 +5338,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380377</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5249,6 +5454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380380</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5360,6 +5570,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380667</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5471,6 +5686,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383027</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5582,6 +5802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380376</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5693,6 +5918,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380379</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5804,6 +6034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380668</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5931,6 +6166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384631</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6042,6 +6282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380378</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6153,6 +6398,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380382</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6264,6 +6514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383280</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6375,6 +6630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383276</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6482,6 +6742,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135374074</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6593,6 +6858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383278</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6704,6 +6974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383279</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6827,6 +7102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382693</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6924,6 +7204,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92515</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7035,6 +7320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380357</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7151,6 +7441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380644</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7262,6 +7557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380651</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7373,6 +7673,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383012</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7475,6 +7780,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/309457</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7586,6 +7896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380648</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7697,6 +8012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384615</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7808,6 +8128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380361</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7919,6 +8244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380645</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8030,6 +8360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384617</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8141,6 +8476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380646</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8252,6 +8592,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383291</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8363,6 +8708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380358</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8474,6 +8824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383013</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8581,6 +8936,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372813</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8688,6 +9048,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372935</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8795,6 +9160,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372979</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8911,6 +9281,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380653</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9022,6 +9397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383267</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9133,6 +9513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383268</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9244,6 +9629,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383272</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9355,6 +9745,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383275</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9466,6 +9861,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380652</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9573,6 +9973,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135371985</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9680,6 +10085,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372847</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9791,6 +10201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380650</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9902,6 +10317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380654</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10013,6 +10433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383010</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10124,6 +10549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383011</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10235,6 +10665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383014</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10346,6 +10781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383017</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10457,6 +10897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380360</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10568,6 +11013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383284</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10679,6 +11129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383285</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10790,6 +11245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380647</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10901,6 +11361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382692</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11012,6 +11477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383288</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11123,6 +11593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383273</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11234,6 +11709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383287</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11350,6 +11830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383269</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11466,6 +11951,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383283</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11582,6 +12072,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383290</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11698,6 +12193,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135371874</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11819,6 +12319,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135373243</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11940,6 +12445,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135376029</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12051,6 +12561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380655</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12162,6 +12677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380656</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12273,6 +12793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383289</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12384,6 +12909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383286</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12491,6 +13021,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135373563</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12598,6 +13133,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372100</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12705,6 +13245,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135372226</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12812,6 +13357,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135373694</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12923,6 +13473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380359</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13034,6 +13589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380362</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13145,6 +13705,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380649</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13256,6 +13821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383015</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13367,6 +13937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383274</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13478,6 +14053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380395</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13589,6 +14169,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380387</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13700,6 +14285,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380673</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13811,6 +14401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383029</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13922,6 +14517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380675</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14019,6 +14619,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92516</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14130,6 +14735,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380355</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14241,6 +14851,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380672</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14352,6 +14967,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380677</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14463,6 +15083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384635</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14574,6 +15199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384640</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14685,6 +15315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384636</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14796,6 +15431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380391</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14907,6 +15547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384633</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15023,6 +15668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380393</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15134,6 +15784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380384</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15245,6 +15900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383030</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15356,6 +16016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383264</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15467,6 +16132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380634</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15578,6 +16248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383031</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15689,6 +16364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380383</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15800,6 +16480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380385</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15911,6 +16596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380386</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16022,6 +16712,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380636</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16133,6 +16828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380643</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16244,6 +16944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380354</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16355,6 +17060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383262</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16466,6 +17176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380397</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16587,6 +17302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384616</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16708,6 +17428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384638</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16819,6 +17544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380670</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16930,6 +17660,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383263</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17041,6 +17776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384637</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17152,6 +17892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380674</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17263,6 +18008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380676</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17374,6 +18124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380635</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17481,6 +18236,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135371686</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17592,6 +18352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380388</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17703,6 +18468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380398</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17814,6 +18584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380633</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17925,6 +18700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380678</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18036,6 +18816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383265</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18133,6 +18918,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122812</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18230,6 +19020,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92517</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18327,6 +19122,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85297</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18438,6 +19238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380680</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18549,6 +19354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380351</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18660,6 +19470,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380352</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18771,6 +19586,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380402</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18882,6 +19702,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380625</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18993,6 +19818,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380631</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19104,6 +19934,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380638</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19215,6 +20050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380639</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19326,6 +20166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380353</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19437,6 +20282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380403</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19548,6 +20398,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380679</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19659,6 +20514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380627</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19770,6 +20630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380641</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19881,6 +20746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383032</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19992,6 +20862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380401</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20120,6 +20995,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382694</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20236,6 +21116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380632</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20347,6 +21232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380637</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20458,6 +21348,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383292</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20569,6 +21464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380682</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20680,6 +21580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380400</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20791,6 +21696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380626</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20893,6 +21803,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2042520</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21004,6 +21919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382212</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21115,6 +22035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382961</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21212,6 +22137,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490387</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21309,6 +22239,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91817575</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21420,6 +22355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382962</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21531,6 +22471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382963</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21642,6 +22587,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380624</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21753,6 +22703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380623</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21864,6 +22819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380622</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21980,6 +22940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383261</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22103,6 +23068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382695</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22212,6 +23182,11 @@
       <c r="AY195" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382213</t>
         </is>
       </c>
     </row>
@@ -22323,6 +23298,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55275159</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22434,6 +23414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383294</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22545,6 +23530,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380404</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22656,6 +23646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383134</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22767,6 +23762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383113</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22878,6 +23878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383111</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22989,6 +23994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383112</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23100,6 +24110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383114</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23211,6 +24226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383133</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23322,6 +24342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383137</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23433,6 +24458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382100</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23544,6 +24574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382101</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23655,6 +24690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382194</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23766,6 +24806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383136</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23882,6 +24927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382196</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23993,6 +25043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382951</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24104,6 +25159,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382195</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24215,6 +25275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382197</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24326,6 +25391,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382949</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24437,6 +25507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382948</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24548,6 +25623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383110</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24659,6 +25739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383117</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24770,6 +25855,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383119</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24881,6 +25971,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377466</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24993,6 +26088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382206</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25104,6 +26204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377473</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25215,6 +26320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377376</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25326,6 +26436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377387</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25437,6 +26552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377497</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25548,6 +26668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379379</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25659,6 +26784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379385</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25770,6 +26900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382208</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25871,6 +27006,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383692</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25982,6 +27122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377396</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26093,6 +27238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377400</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26204,6 +27354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377468</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26315,6 +27470,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379373</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26426,6 +27586,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379374</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26537,6 +27702,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379376</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26648,6 +27818,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383138</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26759,6 +27934,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377481</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26871,6 +28051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382207</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26982,6 +28167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377467</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27091,6 +28281,11 @@
       <c r="AY239" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377494</t>
         </is>
       </c>
     </row>
@@ -27228,6 +28423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135547424</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27339,6 +28539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379387</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27450,6 +28655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377485</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27561,6 +28771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377107</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27672,6 +28887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382303</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27783,6 +29003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377083</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27894,6 +29119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377084</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28005,6 +29235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377086</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28116,6 +29351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377102</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28227,6 +29467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377109</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28338,6 +29583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377371</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28447,6 +29697,11 @@
       <c r="AY251" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377378</t>
         </is>
       </c>
     </row>
@@ -28564,6 +29819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377388</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28675,6 +29935,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377391</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28786,6 +30051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377392</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28897,6 +30167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377460</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29008,6 +30283,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377461</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29119,6 +30399,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377465</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29230,6 +30515,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377477</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29341,6 +30631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377482</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29452,6 +30747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377483</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29563,6 +30863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377487</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29674,6 +30979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377489</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29785,6 +31095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379369</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29896,6 +31211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379386</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30007,6 +31327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382209</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30118,6 +31443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382302</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30229,6 +31559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382957</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30330,6 +31665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383689</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30441,6 +31781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377369</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30552,6 +31897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377383</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30663,6 +32013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377384</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30774,6 +32129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377395</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30885,6 +32245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382200</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30996,6 +32361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382952</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31107,6 +32477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377393</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -31218,6 +32593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377479</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31329,6 +32709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382202</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31440,6 +32825,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383141</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31552,6 +32942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377087</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31663,6 +33058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377370</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31774,6 +33174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377375</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31885,6 +33290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377394</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31996,6 +33406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377398</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32107,6 +33522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377492</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32218,6 +33638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379381</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32329,6 +33754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379382</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32440,6 +33870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379388</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32541,6 +33976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383691</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32642,6 +34082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383697</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32753,6 +34198,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377091</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32864,6 +34314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377475</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32975,6 +34430,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377476</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -33086,6 +34546,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382298</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33197,6 +34662,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383139</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33308,6 +34778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383140</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33419,6 +34894,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382097</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33530,6 +35010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377379</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33642,6 +35127,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382201</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33758,6 +35248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377390</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33874,6 +35369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382203</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33990,6 +35490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382204</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34102,6 +35607,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377380</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34213,6 +35723,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382954</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34314,6 +35829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383687</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34425,6 +35945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379371</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34536,6 +36061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377085</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34645,6 +36175,11 @@
       <c r="AY307" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377110</t>
         </is>
       </c>
     </row>
@@ -34763,6 +36298,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377111</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34874,6 +36414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377112</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34985,6 +36530,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377114</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35096,6 +36646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377478</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35207,6 +36762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377488</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35318,6 +36878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382937</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35429,6 +36994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382956</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35540,6 +37110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382959</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35656,6 +37231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377092</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35767,6 +37347,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377093</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35883,6 +37468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377094</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35992,6 +37582,11 @@
       <c r="AY319" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377095</t>
         </is>
       </c>
     </row>
@@ -36119,6 +37714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377097</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36230,6 +37830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377098</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36341,6 +37946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377100</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36452,6 +38062,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377108</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36563,6 +38178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377471</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36674,6 +38294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377472</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36794,6 +38419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377480</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36910,6 +38540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382090</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37021,6 +38656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382094</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37142,6 +38782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382299</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37258,6 +38903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382300</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37369,6 +39019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382939</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37480,6 +39135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382940</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37591,6 +39251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382941</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37702,6 +39367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382944</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37813,6 +39483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382946</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37924,6 +39599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382947</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -38035,6 +39715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382960</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -38142,6 +39827,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385107</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38253,6 +39943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377089</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38364,6 +40059,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377463</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38475,6 +40175,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379370</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38586,6 +40291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377096</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38697,6 +40407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377464</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38808,6 +40523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382096</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38919,6 +40639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382945</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -39030,6 +40755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379378</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -39141,6 +40871,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377104</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -39252,6 +40987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377374</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -39363,6 +41103,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377389</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -39474,6 +41219,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377484</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39585,6 +41335,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379372</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39696,6 +41451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379380</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39807,6 +41567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379383</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -39918,6 +41683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382089</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -40029,6 +41799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382095</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -40140,6 +41915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382099</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -40251,6 +42031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382205</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40362,6 +42147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382938</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40473,6 +42263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382942</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40584,6 +42379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382953</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40685,6 +42485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383686</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40786,6 +42591,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383693</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -40887,6 +42697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383695</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -40988,6 +42803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383690</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -41099,6 +42919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377090</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -41210,6 +43035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377462</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41321,6 +43151,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379384</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41432,6 +43267,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377372</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -41543,6 +43383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377490</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41649,6 +43494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377399</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41760,6 +43610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377407</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -41871,6 +43726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377411</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -41982,6 +43842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377425</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -42093,6 +43958,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377402</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -42190,6 +44060,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490385</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -42287,6 +44162,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490388</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42384,6 +44264,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/490389</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42495,6 +44380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377499</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42606,6 +44496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383144</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42717,6 +44612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383147</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -42828,6 +44728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383149</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -42939,6 +44844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377136</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -43050,6 +44960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377422</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -43161,6 +45076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377403</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -43272,6 +45192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377415</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -43383,6 +45308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377423</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -43494,6 +45424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377501</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43605,6 +45540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377506</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -43716,6 +45656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379363</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -43827,6 +45772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379394</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -43938,6 +45888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379399</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -44049,6 +46004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382965</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -44160,6 +46120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383152</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -44271,6 +46236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377408</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -44382,6 +46352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377420</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -44493,6 +46468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379390</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -44604,6 +46584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379393</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -44715,6 +46700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379395</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -44826,6 +46816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379398</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -44937,6 +46932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383146</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -45048,6 +47048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377125</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -45159,6 +47164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377508</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -45270,6 +47280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377509</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -45381,6 +47396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377518</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -45492,6 +47512,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377519</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -45603,6 +47628,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377512</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -45714,6 +47744,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379397</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -45825,6 +47860,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377510</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -45936,6 +47976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377513</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -46047,6 +48092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377517</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -46158,6 +48208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377520</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -46269,6 +48324,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377511</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -46380,6 +48440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377521</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -46491,6 +48556,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379401</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -46602,6 +48672,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377404</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -46718,6 +48793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377143</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -46834,6 +48914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377409</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -46950,6 +49035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382214</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -47061,6 +49151,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382966</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -47177,6 +49272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379364</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -47288,6 +49388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377140</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -47399,6 +49504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379389</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -47510,6 +49620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383143</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -47621,6 +49736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383145</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -47732,6 +49852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383151</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -47843,6 +49968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377126</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -47954,6 +50084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382964</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -48065,6 +50200,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377401</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -48176,6 +50316,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379396</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -48287,6 +50432,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383150</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -48398,6 +50548,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377405</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -48509,6 +50664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377416</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -48620,6 +50780,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377502</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -48731,6 +50896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377505</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -48842,6 +51012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377118</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -48953,6 +51128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377119</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -49064,6 +51244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377121</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -49175,6 +51360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377130</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -49286,6 +51476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377137</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -49397,6 +51592,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377138</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -49508,6 +51708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377139</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -49619,6 +51824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377144</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -49730,6 +51940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377410</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -49841,6 +52056,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377414</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -49952,6 +52172,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377503</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -50063,6 +52288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379365</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -50174,6 +52404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379400</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -50285,6 +52520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382967</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -50396,6 +52636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382968</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -50497,6 +52742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383698</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -50603,6 +52853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377413</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -50709,6 +52964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377419</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -50815,6 +53075,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377500</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -50921,6 +53186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377514</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -51032,6 +53302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377145</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -51143,6 +53418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383123</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -51254,6 +53534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383120</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -51365,6 +53650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383129</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -51476,6 +53766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383125</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -51587,6 +53882,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383126</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -51698,6 +53998,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383128</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -51809,6 +54114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383122</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -51920,6 +54230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382092</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -52031,6 +54346,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383107</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -52142,6 +54462,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383124</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -52253,6 +54578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382093</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -52364,6 +54694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383130</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -52475,6 +54810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383121</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -52586,6 +54926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383127</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -52697,6 +55042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383132</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -52808,6 +55158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382296</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -52919,6 +55274,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377080</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -53030,6 +55390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377081</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -53141,6 +55506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379368</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -53252,6 +55622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382936</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -53363,6 +55738,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377079</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -53474,6 +55854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377442</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -53585,6 +55970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377532</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -53696,6 +56086,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379350</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -53797,6 +56192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383684</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -53908,6 +56308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377523</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -54024,6 +56429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377522</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -54135,6 +56545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377347</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -54246,6 +56661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377350</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -54357,6 +56777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379355</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -54468,6 +56893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377070</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -54579,6 +57009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377525</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -54690,6 +57125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379356</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -54801,6 +57241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379358</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -54912,6 +57357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379360</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -55023,6 +57473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377074</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -55134,6 +57589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377348</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -55245,6 +57705,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377351</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -55356,6 +57821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377368</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -55467,6 +57937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377439</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -55578,6 +58053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377448</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -55689,6 +58169,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377529</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -55800,6 +58285,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377530</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -55911,6 +58401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377533</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -56022,6 +58517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379351</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -56123,6 +58623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383685</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -56234,6 +58739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377363</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -56345,6 +58855,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377367</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -56456,6 +58971,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377441</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -56567,6 +59087,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377444</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -56678,6 +59203,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379352</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -56789,6 +59319,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379354</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -56900,6 +59435,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382294</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -57011,6 +59551,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382295</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -57127,6 +59672,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377455</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -57238,6 +59788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377361</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -57349,6 +59904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377071</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -57460,6 +60020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377353</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -57571,6 +60136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377527</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -57682,6 +60252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379359</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -57793,6 +60368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379361</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -57904,6 +60484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377447</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -58015,6 +60600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377526</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -58131,6 +60721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377443</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -58242,6 +60837,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379362</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -58353,6 +60953,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377355</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -58464,6 +61069,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377451</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -58565,6 +61175,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383683</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -58676,6 +61291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377354</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -58787,6 +61407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377453</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -58898,6 +61523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377360</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -59009,6 +61639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377458</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -59120,6 +61755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377524</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -59231,6 +61871,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377364</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -59342,6 +61987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377436</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -59453,6 +62103,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377449</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -59562,6 +62217,11 @@
       <c r="AY532" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377076</t>
         </is>
       </c>
     </row>
@@ -59679,6 +62339,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377077</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -59790,6 +62455,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377440</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -59901,6 +62571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379353</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -60007,6 +62682,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377446</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -60118,8 +62798,551 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135377456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -28415,7 +28415,7 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, Cajsa Björkén, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Cajsa Björkén, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Jörgen Sundin, Linda Nordström</t>
+          <t>Katharina Radloff, Linda Nordström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Linda Nordström, Jörgen Sundin</t>
+          <t>Katharina Radloff, Jörgen Sundin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Cajsa Björkén, Moa Turid Lövdahl</t>
+          <t>Moa Turid Lövdahl, Cajsa Björkén, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135380374</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135387752</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135380364</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>135380366</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135384627</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135384630</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135384620</v>
       </c>
       <c r="B8" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>135384621</v>
       </c>
       <c r="B9" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135384624</v>
       </c>
       <c r="B10" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135380660</v>
       </c>
       <c r="B11" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135380363</v>
       </c>
       <c r="B12" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135380367</v>
       </c>
       <c r="B13" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135380368</v>
       </c>
       <c r="B14" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135380375</v>
       </c>
       <c r="B15" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135380664</v>
       </c>
       <c r="B16" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135384623</v>
       </c>
       <c r="B17" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135380657</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135380658</v>
       </c>
       <c r="B19" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135380371</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>135380661</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>135380663</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>135383020</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135383023</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>135380369</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>135383022</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>135380665</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>135384628</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135384629</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>135383025</v>
       </c>
       <c r="B31" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>135384619</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135384626</v>
       </c>
       <c r="B33" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>135380370</v>
       </c>
       <c r="B34" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>135380373</v>
       </c>
       <c r="B35" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>135380659</v>
       </c>
       <c r="B36" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>135383021</v>
       </c>
       <c r="B37" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>135383024</v>
       </c>
       <c r="B38" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>135383026</v>
       </c>
       <c r="B39" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>135384632</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>135380377</v>
       </c>
       <c r="B41" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>135380380</v>
       </c>
       <c r="B42" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>135380667</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135383027</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>135380376</v>
       </c>
       <c r="B45" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>135380379</v>
       </c>
       <c r="B46" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>135380668</v>
       </c>
       <c r="B47" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>135384631</v>
       </c>
       <c r="B48" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135380378</v>
       </c>
       <c r="B49" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>135380382</v>
       </c>
       <c r="B50" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>135383280</v>
       </c>
       <c r="B51" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>135383276</v>
       </c>
       <c r="B52" t="n">
-        <v>93265</v>
+        <v>93307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>135374074</v>
       </c>
       <c r="B53" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>135383278</v>
       </c>
       <c r="B54" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>135383279</v>
       </c>
       <c r="B55" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>135382693</v>
       </c>
       <c r="B56" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>135380357</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>135380644</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135380651</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135383012</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>135380648</v>
       </c>
       <c r="B63" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135384615</v>
       </c>
       <c r="B64" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>135380361</v>
       </c>
       <c r="B65" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135380645</v>
       </c>
       <c r="B66" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>135384617</v>
       </c>
       <c r="B67" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135380646</v>
       </c>
       <c r="B68" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>135383291</v>
       </c>
       <c r="B69" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>135380358</v>
       </c>
       <c r="B70" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>135383013</v>
       </c>
       <c r="B71" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135372813</v>
       </c>
       <c r="B72" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135372935</v>
       </c>
       <c r="B73" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>135372979</v>
       </c>
       <c r="B74" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>135380653</v>
       </c>
       <c r="B75" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>135383267</v>
       </c>
       <c r="B76" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135383268</v>
       </c>
       <c r="B77" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>135383272</v>
       </c>
       <c r="B78" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>135383275</v>
       </c>
       <c r="B79" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>135380652</v>
       </c>
       <c r="B80" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>135371985</v>
       </c>
       <c r="B81" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135372847</v>
       </c>
       <c r="B82" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>135380650</v>
       </c>
       <c r="B83" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>135380654</v>
       </c>
       <c r="B84" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>135383010</v>
       </c>
       <c r="B85" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>135383011</v>
       </c>
       <c r="B86" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>135383014</v>
       </c>
       <c r="B87" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135383017</v>
       </c>
       <c r="B88" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135380360</v>
       </c>
       <c r="B89" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>135383284</v>
       </c>
       <c r="B90" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135383285</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>135380647</v>
       </c>
       <c r="B92" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>135382692</v>
       </c>
       <c r="B93" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135383288</v>
       </c>
       <c r="B94" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>135383273</v>
       </c>
       <c r="B95" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135383287</v>
       </c>
       <c r="B96" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135383269</v>
       </c>
       <c r="B97" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>135383283</v>
       </c>
       <c r="B98" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>135383290</v>
       </c>
       <c r="B99" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>135371874</v>
       </c>
       <c r="B100" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>135373243</v>
       </c>
       <c r="B101" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>135376029</v>
       </c>
       <c r="B102" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>135380655</v>
       </c>
       <c r="B103" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>135380656</v>
       </c>
       <c r="B104" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>135383289</v>
       </c>
       <c r="B105" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>135383286</v>
       </c>
       <c r="B106" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>135373563</v>
       </c>
       <c r="B107" t="n">
-        <v>79050</v>
+        <v>79088</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>135372100</v>
       </c>
       <c r="B108" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>135372226</v>
       </c>
       <c r="B109" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>135373694</v>
       </c>
       <c r="B110" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>135380359</v>
       </c>
       <c r="B111" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>135380362</v>
       </c>
       <c r="B112" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>135380649</v>
       </c>
       <c r="B113" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>135383015</v>
       </c>
       <c r="B114" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>135383274</v>
       </c>
       <c r="B115" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>135380395</v>
       </c>
       <c r="B116" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>135380387</v>
       </c>
       <c r="B117" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>135380673</v>
       </c>
       <c r="B118" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>135383029</v>
       </c>
       <c r="B119" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>135380675</v>
       </c>
       <c r="B120" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>135380355</v>
       </c>
       <c r="B122" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>135380672</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>135380677</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135384635</v>
       </c>
       <c r="B125" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>135384640</v>
       </c>
       <c r="B126" t="n">
-        <v>92559</v>
+        <v>92601</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>135384636</v>
       </c>
       <c r="B127" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>135380391</v>
       </c>
       <c r="B128" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135384633</v>
       </c>
       <c r="B129" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>135380393</v>
       </c>
       <c r="B130" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>135380384</v>
       </c>
       <c r="B131" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>135383030</v>
       </c>
       <c r="B132" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>135383264</v>
       </c>
       <c r="B133" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>135380634</v>
       </c>
       <c r="B134" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135383031</v>
       </c>
       <c r="B135" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>135380383</v>
       </c>
       <c r="B136" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>135380385</v>
       </c>
       <c r="B137" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>135380386</v>
       </c>
       <c r="B138" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>135380636</v>
       </c>
       <c r="B139" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>135380643</v>
       </c>
       <c r="B140" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>135380354</v>
       </c>
       <c r="B141" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>135383262</v>
       </c>
       <c r="B142" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>135380397</v>
       </c>
       <c r="B143" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>135384616</v>
       </c>
       <c r="B144" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>135384638</v>
       </c>
       <c r="B145" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135380670</v>
       </c>
       <c r="B146" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>135383263</v>
       </c>
       <c r="B147" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>135384637</v>
       </c>
       <c r="B148" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>135380674</v>
       </c>
       <c r="B149" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>135380676</v>
       </c>
       <c r="B150" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>135380635</v>
       </c>
       <c r="B151" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>135371686</v>
       </c>
       <c r="B152" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>135380388</v>
       </c>
       <c r="B153" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135380398</v>
       </c>
       <c r="B154" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>135380633</v>
       </c>
       <c r="B155" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>135380678</v>
       </c>
       <c r="B156" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>135383265</v>
       </c>
       <c r="B157" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>135380680</v>
       </c>
       <c r="B161" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>135380351</v>
       </c>
       <c r="B162" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>135380352</v>
       </c>
       <c r="B163" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>135380402</v>
       </c>
       <c r="B164" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>135380625</v>
       </c>
       <c r="B165" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>135380631</v>
       </c>
       <c r="B166" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>135380638</v>
       </c>
       <c r="B167" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>135380639</v>
       </c>
       <c r="B168" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>135380353</v>
       </c>
       <c r="B169" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>135380403</v>
       </c>
       <c r="B170" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>135380679</v>
       </c>
       <c r="B171" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>135380627</v>
       </c>
       <c r="B172" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>135380641</v>
       </c>
       <c r="B173" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>135383032</v>
       </c>
       <c r="B174" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>135380401</v>
       </c>
       <c r="B175" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>135382694</v>
       </c>
       <c r="B176" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>135380632</v>
       </c>
       <c r="B177" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>135380637</v>
       </c>
       <c r="B178" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>135383292</v>
       </c>
       <c r="B179" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>135380682</v>
       </c>
       <c r="B180" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>135380400</v>
       </c>
       <c r="B181" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>135380626</v>
       </c>
       <c r="B182" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>135382212</v>
       </c>
       <c r="B184" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>135382961</v>
       </c>
       <c r="B185" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>135382962</v>
       </c>
       <c r="B188" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>135382963</v>
       </c>
       <c r="B189" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>135380624</v>
       </c>
       <c r="B190" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>135380623</v>
       </c>
       <c r="B191" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>135380622</v>
       </c>
       <c r="B192" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>135383261</v>
       </c>
       <c r="B193" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>135382695</v>
       </c>
       <c r="B194" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>135382213</v>
       </c>
       <c r="B195" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>135383294</v>
       </c>
       <c r="B197" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>135380404</v>
       </c>
       <c r="B198" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>135383134</v>
       </c>
       <c r="B199" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>135383113</v>
       </c>
       <c r="B200" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>135383111</v>
       </c>
       <c r="B201" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>135383112</v>
       </c>
       <c r="B202" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>135383114</v>
       </c>
       <c r="B203" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>135383133</v>
       </c>
       <c r="B204" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>135383137</v>
       </c>
       <c r="B205" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>135382100</v>
       </c>
       <c r="B206" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>135382101</v>
       </c>
       <c r="B207" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>135382194</v>
       </c>
       <c r="B208" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>135383136</v>
       </c>
       <c r="B209" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>135382196</v>
       </c>
       <c r="B210" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>135382951</v>
       </c>
       <c r="B211" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>135382195</v>
       </c>
       <c r="B212" t="n">
-        <v>56539</v>
+        <v>56544</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>135382197</v>
       </c>
       <c r="B213" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>135382949</v>
       </c>
       <c r="B214" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>135382948</v>
       </c>
       <c r="B215" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>135383110</v>
       </c>
       <c r="B216" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>135383117</v>
       </c>
       <c r="B217" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>135383119</v>
       </c>
       <c r="B218" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>135377466</v>
       </c>
       <c r="B219" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>135382206</v>
       </c>
       <c r="B220" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>135377473</v>
       </c>
       <c r="B221" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>135377376</v>
       </c>
       <c r="B222" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>135377387</v>
       </c>
       <c r="B223" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>135377497</v>
       </c>
       <c r="B224" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>135379379</v>
       </c>
       <c r="B225" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>135379385</v>
       </c>
       <c r="B226" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>135382208</v>
       </c>
       <c r="B227" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>135383692</v>
       </c>
       <c r="B228" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>135377396</v>
       </c>
       <c r="B229" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>135377400</v>
       </c>
       <c r="B230" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>135377468</v>
       </c>
       <c r="B231" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>135379373</v>
       </c>
       <c r="B232" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>135379374</v>
       </c>
       <c r="B233" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>135379376</v>
       </c>
       <c r="B234" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>135383138</v>
       </c>
       <c r="B235" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>135377481</v>
       </c>
       <c r="B236" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>135382207</v>
       </c>
       <c r="B237" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>135377467</v>
       </c>
       <c r="B238" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>135377494</v>
       </c>
       <c r="B239" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>135547424</v>
       </c>
       <c r="B240" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>135379387</v>
       </c>
       <c r="B241" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>135377485</v>
       </c>
       <c r="B242" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>135377107</v>
       </c>
       <c r="B243" t="n">
-        <v>87625</v>
+        <v>87665</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>135382303</v>
       </c>
       <c r="B244" t="n">
-        <v>87625</v>
+        <v>87665</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>135377083</v>
       </c>
       <c r="B245" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>135377084</v>
       </c>
       <c r="B246" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>135377086</v>
       </c>
       <c r="B247" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>135377102</v>
       </c>
       <c r="B248" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>135377109</v>
       </c>
       <c r="B249" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>135377371</v>
       </c>
       <c r="B250" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>135377378</v>
       </c>
       <c r="B251" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>135377388</v>
       </c>
       <c r="B252" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>135377391</v>
       </c>
       <c r="B253" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>135377392</v>
       </c>
       <c r="B254" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>135377460</v>
       </c>
       <c r="B255" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>135377461</v>
       </c>
       <c r="B256" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>135377465</v>
       </c>
       <c r="B257" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>135377477</v>
       </c>
       <c r="B258" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>135377482</v>
       </c>
       <c r="B259" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>135377483</v>
       </c>
       <c r="B260" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>135377487</v>
       </c>
       <c r="B261" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>135377489</v>
       </c>
       <c r="B262" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>135379369</v>
       </c>
       <c r="B263" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>135379386</v>
       </c>
       <c r="B264" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>135382209</v>
       </c>
       <c r="B265" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>135382302</v>
       </c>
       <c r="B266" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>135382957</v>
       </c>
       <c r="B267" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>135383689</v>
       </c>
       <c r="B268" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>135377369</v>
       </c>
       <c r="B269" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>135377383</v>
       </c>
       <c r="B270" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>135377384</v>
       </c>
       <c r="B271" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>135377395</v>
       </c>
       <c r="B272" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>135382200</v>
       </c>
       <c r="B273" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>135382952</v>
       </c>
       <c r="B274" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>135377393</v>
       </c>
       <c r="B275" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>135377479</v>
       </c>
       <c r="B276" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>135382202</v>
       </c>
       <c r="B277" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>135383141</v>
       </c>
       <c r="B278" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>135377087</v>
       </c>
       <c r="B279" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>135377370</v>
       </c>
       <c r="B280" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>135377375</v>
       </c>
       <c r="B281" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>135377394</v>
       </c>
       <c r="B282" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>135377398</v>
       </c>
       <c r="B283" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>135377492</v>
       </c>
       <c r="B284" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>135379381</v>
       </c>
       <c r="B285" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>135379382</v>
       </c>
       <c r="B286" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>135379388</v>
       </c>
       <c r="B287" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>135383691</v>
       </c>
       <c r="B288" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>135383697</v>
       </c>
       <c r="B289" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>135377091</v>
       </c>
       <c r="B290" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>135377475</v>
       </c>
       <c r="B291" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>135377476</v>
       </c>
       <c r="B292" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>135382298</v>
       </c>
       <c r="B293" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>135383139</v>
       </c>
       <c r="B294" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>135383140</v>
       </c>
       <c r="B295" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>135382097</v>
       </c>
       <c r="B296" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>135377379</v>
       </c>
       <c r="B297" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>135382201</v>
       </c>
       <c r="B298" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>135377390</v>
       </c>
       <c r="B299" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>135382203</v>
       </c>
       <c r="B300" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>135382204</v>
       </c>
       <c r="B301" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>135377380</v>
       </c>
       <c r="B302" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>135382954</v>
       </c>
       <c r="B303" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>135383687</v>
       </c>
       <c r="B304" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>135379371</v>
       </c>
       <c r="B305" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>135377085</v>
       </c>
       <c r="B306" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>135377110</v>
       </c>
       <c r="B307" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>135377111</v>
       </c>
       <c r="B308" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>135377112</v>
       </c>
       <c r="B309" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>135377114</v>
       </c>
       <c r="B310" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>135377478</v>
       </c>
       <c r="B311" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>135377488</v>
       </c>
       <c r="B312" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>135382937</v>
       </c>
       <c r="B313" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>135382956</v>
       </c>
       <c r="B314" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135382959</v>
       </c>
       <c r="B315" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>135377092</v>
       </c>
       <c r="B316" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135377093</v>
       </c>
       <c r="B317" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135377094</v>
       </c>
       <c r="B318" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>135377095</v>
       </c>
       <c r="B319" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>135377097</v>
       </c>
       <c r="B320" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>135377098</v>
       </c>
       <c r="B321" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>135377100</v>
       </c>
       <c r="B322" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>135377108</v>
       </c>
       <c r="B323" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>135377471</v>
       </c>
       <c r="B324" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>135377472</v>
       </c>
       <c r="B325" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>135377480</v>
       </c>
       <c r="B326" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>135382090</v>
       </c>
       <c r="B327" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>135382094</v>
       </c>
       <c r="B328" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>135382299</v>
       </c>
       <c r="B329" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>135382300</v>
       </c>
       <c r="B330" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>135382939</v>
       </c>
       <c r="B331" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>135382940</v>
       </c>
       <c r="B332" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>135382941</v>
       </c>
       <c r="B333" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>135382944</v>
       </c>
       <c r="B334" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>135382946</v>
       </c>
       <c r="B335" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>135382947</v>
       </c>
       <c r="B336" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>135382960</v>
       </c>
       <c r="B337" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>135385107</v>
       </c>
       <c r="B338" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>135377089</v>
       </c>
       <c r="B339" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>135377463</v>
       </c>
       <c r="B340" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>135379370</v>
       </c>
       <c r="B341" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>135377096</v>
       </c>
       <c r="B342" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>135377464</v>
       </c>
       <c r="B343" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>135382096</v>
       </c>
       <c r="B344" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>135382945</v>
       </c>
       <c r="B345" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>135379378</v>
       </c>
       <c r="B346" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>135377104</v>
       </c>
       <c r="B347" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>135377374</v>
       </c>
       <c r="B348" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>135377389</v>
       </c>
       <c r="B349" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>135377484</v>
       </c>
       <c r="B350" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>135379372</v>
       </c>
       <c r="B351" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>135379380</v>
       </c>
       <c r="B352" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>135379383</v>
       </c>
       <c r="B353" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>135382089</v>
       </c>
       <c r="B354" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>135382095</v>
       </c>
       <c r="B355" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>135382099</v>
       </c>
       <c r="B356" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>135382205</v>
       </c>
       <c r="B357" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>135382938</v>
       </c>
       <c r="B358" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>135382942</v>
       </c>
       <c r="B359" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>135382953</v>
       </c>
       <c r="B360" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>135383686</v>
       </c>
       <c r="B361" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>135383693</v>
       </c>
       <c r="B362" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>135383695</v>
       </c>
       <c r="B363" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>135383690</v>
       </c>
       <c r="B364" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>135377090</v>
       </c>
       <c r="B365" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>135377462</v>
       </c>
       <c r="B366" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>135379384</v>
       </c>
       <c r="B367" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>135377372</v>
       </c>
       <c r="B368" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>135377490</v>
       </c>
       <c r="B369" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>135377399</v>
       </c>
       <c r="B370" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>135377407</v>
       </c>
       <c r="B371" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>135377411</v>
       </c>
       <c r="B372" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>135377425</v>
       </c>
       <c r="B373" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>135377402</v>
       </c>
       <c r="B374" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>135377499</v>
       </c>
       <c r="B378" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>135383144</v>
       </c>
       <c r="B379" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>135383147</v>
       </c>
       <c r="B380" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>135383149</v>
       </c>
       <c r="B381" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>135377136</v>
       </c>
       <c r="B382" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>135377422</v>
       </c>
       <c r="B383" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>135377403</v>
       </c>
       <c r="B384" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>135377415</v>
       </c>
       <c r="B385" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>135377423</v>
       </c>
       <c r="B386" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>135377501</v>
       </c>
       <c r="B387" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>135377506</v>
       </c>
       <c r="B388" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>135379363</v>
       </c>
       <c r="B389" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>135379394</v>
       </c>
       <c r="B390" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>135379399</v>
       </c>
       <c r="B391" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>135382965</v>
       </c>
       <c r="B392" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>135383152</v>
       </c>
       <c r="B393" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>135377408</v>
       </c>
       <c r="B394" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>135377420</v>
       </c>
       <c r="B395" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>135379390</v>
       </c>
       <c r="B396" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>135379393</v>
       </c>
       <c r="B397" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>135379395</v>
       </c>
       <c r="B398" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>135379398</v>
       </c>
       <c r="B399" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>135383146</v>
       </c>
       <c r="B400" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>135377125</v>
       </c>
       <c r="B401" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>135377508</v>
       </c>
       <c r="B402" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>135377509</v>
       </c>
       <c r="B403" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>135377518</v>
       </c>
       <c r="B404" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>135377519</v>
       </c>
       <c r="B405" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>135377512</v>
       </c>
       <c r="B406" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>135379397</v>
       </c>
       <c r="B407" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>135377510</v>
       </c>
       <c r="B408" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>135377513</v>
       </c>
       <c r="B409" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>135377517</v>
       </c>
       <c r="B410" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>135377520</v>
       </c>
       <c r="B411" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>135377511</v>
       </c>
       <c r="B412" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>135377521</v>
       </c>
       <c r="B413" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>135379401</v>
       </c>
       <c r="B414" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>135377404</v>
       </c>
       <c r="B415" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>135377143</v>
       </c>
       <c r="B416" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>135377409</v>
       </c>
       <c r="B417" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>135382214</v>
       </c>
       <c r="B418" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>135382966</v>
       </c>
       <c r="B419" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>135379364</v>
       </c>
       <c r="B420" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>135377140</v>
       </c>
       <c r="B421" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>135379389</v>
       </c>
       <c r="B422" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>135383143</v>
       </c>
       <c r="B423" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>135383145</v>
       </c>
       <c r="B424" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>135383151</v>
       </c>
       <c r="B425" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>135377126</v>
       </c>
       <c r="B426" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>135382964</v>
       </c>
       <c r="B427" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>135377401</v>
       </c>
       <c r="B428" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>135379396</v>
       </c>
       <c r="B429" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>135383150</v>
       </c>
       <c r="B430" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>135377405</v>
       </c>
       <c r="B431" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>135377416</v>
       </c>
       <c r="B432" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>135377502</v>
       </c>
       <c r="B433" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>135377505</v>
       </c>
       <c r="B434" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>135377118</v>
       </c>
       <c r="B435" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>135377119</v>
       </c>
       <c r="B436" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>135377121</v>
       </c>
       <c r="B437" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>135377130</v>
       </c>
       <c r="B438" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>135377137</v>
       </c>
       <c r="B439" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>135377138</v>
       </c>
       <c r="B440" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>135377139</v>
       </c>
       <c r="B441" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>135377144</v>
       </c>
       <c r="B442" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>135377410</v>
       </c>
       <c r="B443" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>135377414</v>
       </c>
       <c r="B444" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>135377503</v>
       </c>
       <c r="B445" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>135379365</v>
       </c>
       <c r="B446" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>135379400</v>
       </c>
       <c r="B447" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>135382967</v>
       </c>
       <c r="B448" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>135382968</v>
       </c>
       <c r="B449" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>135383698</v>
       </c>
       <c r="B450" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>135377413</v>
       </c>
       <c r="B451" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>135377419</v>
       </c>
       <c r="B452" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>135377500</v>
       </c>
       <c r="B453" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>135377514</v>
       </c>
       <c r="B454" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>135377145</v>
       </c>
       <c r="B455" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>135383123</v>
       </c>
       <c r="B456" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>135383120</v>
       </c>
       <c r="B457" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>135383129</v>
       </c>
       <c r="B458" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>135383125</v>
       </c>
       <c r="B459" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>135383126</v>
       </c>
       <c r="B460" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -53893,7 +53893,7 @@
         <v>135383128</v>
       </c>
       <c r="B461" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>135383122</v>
       </c>
       <c r="B462" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>135382092</v>
       </c>
       <c r="B463" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54241,7 +54241,7 @@
         <v>135383107</v>
       </c>
       <c r="B464" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>135383124</v>
       </c>
       <c r="B465" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>135382093</v>
       </c>
       <c r="B466" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>135383130</v>
       </c>
       <c r="B467" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>135383121</v>
       </c>
       <c r="B468" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>135383127</v>
       </c>
       <c r="B469" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>135383132</v>
       </c>
       <c r="B470" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>135382296</v>
       </c>
       <c r="B471" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>135377080</v>
       </c>
       <c r="B472" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>135377081</v>
       </c>
       <c r="B473" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>135379368</v>
       </c>
       <c r="B474" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>135382936</v>
       </c>
       <c r="B475" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>135377079</v>
       </c>
       <c r="B476" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>135377442</v>
       </c>
       <c r="B477" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>135377532</v>
       </c>
       <c r="B478" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>135379350</v>
       </c>
       <c r="B479" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>135383684</v>
       </c>
       <c r="B480" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>135377523</v>
       </c>
       <c r="B481" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>135377522</v>
       </c>
       <c r="B482" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>135377347</v>
       </c>
       <c r="B483" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>135377350</v>
       </c>
       <c r="B484" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>135379355</v>
       </c>
       <c r="B485" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>135377070</v>
       </c>
       <c r="B486" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>135377525</v>
       </c>
       <c r="B487" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>135379356</v>
       </c>
       <c r="B488" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>135379358</v>
       </c>
       <c r="B489" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>135379360</v>
       </c>
       <c r="B490" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>135377074</v>
       </c>
       <c r="B491" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -57484,7 +57484,7 @@
         <v>135377348</v>
       </c>
       <c r="B492" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -57600,7 +57600,7 @@
         <v>135377351</v>
       </c>
       <c r="B493" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>135377368</v>
       </c>
       <c r="B494" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>135377439</v>
       </c>
       <c r="B495" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>135377448</v>
       </c>
       <c r="B496" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>135377529</v>
       </c>
       <c r="B497" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58180,7 +58180,7 @@
         <v>135377530</v>
       </c>
       <c r="B498" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>135377533</v>
       </c>
       <c r="B499" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>135379351</v>
       </c>
       <c r="B500" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -58528,7 +58528,7 @@
         <v>135383685</v>
       </c>
       <c r="B501" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>135377363</v>
       </c>
       <c r="B502" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>135377367</v>
       </c>
       <c r="B503" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -58866,7 +58866,7 @@
         <v>135377441</v>
       </c>
       <c r="B504" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         <v>135377444</v>
       </c>
       <c r="B505" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>135379352</v>
       </c>
       <c r="B506" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>135379354</v>
       </c>
       <c r="B507" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>135382294</v>
       </c>
       <c r="B508" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>135382295</v>
       </c>
       <c r="B509" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>135377455</v>
       </c>
       <c r="B510" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59683,7 +59683,7 @@
         <v>135377361</v>
       </c>
       <c r="B511" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>135377071</v>
       </c>
       <c r="B512" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>135377353</v>
       </c>
       <c r="B513" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>135377527</v>
       </c>
       <c r="B514" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>135379359</v>
       </c>
       <c r="B515" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>135379361</v>
       </c>
       <c r="B516" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>135377447</v>
       </c>
       <c r="B517" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>135377526</v>
       </c>
       <c r="B518" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>135377443</v>
       </c>
       <c r="B519" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>135379362</v>
       </c>
       <c r="B520" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>135377355</v>
       </c>
       <c r="B521" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>135377451</v>
       </c>
       <c r="B522" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>135383683</v>
       </c>
       <c r="B523" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>135377354</v>
       </c>
       <c r="B524" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>135377453</v>
       </c>
       <c r="B525" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>135377360</v>
       </c>
       <c r="B526" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>135377458</v>
       </c>
       <c r="B527" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>135377524</v>
       </c>
       <c r="B528" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -61766,7 +61766,7 @@
         <v>135377364</v>
       </c>
       <c r="B529" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -61882,7 +61882,7 @@
         <v>135377436</v>
       </c>
       <c r="B530" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>135377449</v>
       </c>
       <c r="B531" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>135377076</v>
       </c>
       <c r="B532" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>135377077</v>
       </c>
       <c r="B533" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>135377440</v>
       </c>
       <c r="B534" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62466,7 +62466,7 @@
         <v>135379353</v>
       </c>
       <c r="B535" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -62582,7 +62582,7 @@
         <v>135377446</v>
       </c>
       <c r="B536" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135380374</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135387752</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135380364</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>135380366</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135384627</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135384630</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135384620</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>135384621</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135384624</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135380660</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135380363</v>
       </c>
       <c r="B12" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135380367</v>
       </c>
       <c r="B13" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135380368</v>
       </c>
       <c r="B14" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135380375</v>
       </c>
       <c r="B15" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135380664</v>
       </c>
       <c r="B16" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135384623</v>
       </c>
       <c r="B17" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135380657</v>
       </c>
       <c r="B18" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135380658</v>
       </c>
       <c r="B19" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135380371</v>
       </c>
       <c r="B21" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>135380661</v>
       </c>
       <c r="B22" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>135380663</v>
       </c>
       <c r="B23" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>135383020</v>
       </c>
       <c r="B24" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135383023</v>
       </c>
       <c r="B25" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>135380369</v>
       </c>
       <c r="B26" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>135383022</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>135380370</v>
       </c>
       <c r="B34" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>135380373</v>
       </c>
       <c r="B35" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>135380659</v>
       </c>
       <c r="B36" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>135383021</v>
       </c>
       <c r="B37" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>135383024</v>
       </c>
       <c r="B38" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>135383026</v>
       </c>
       <c r="B39" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>135384632</v>
       </c>
       <c r="B40" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>135380377</v>
       </c>
       <c r="B41" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>135380380</v>
       </c>
       <c r="B42" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>135380667</v>
       </c>
       <c r="B43" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135383027</v>
       </c>
       <c r="B44" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>135380376</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>135380379</v>
       </c>
       <c r="B46" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135380378</v>
       </c>
       <c r="B49" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>135380382</v>
       </c>
       <c r="B50" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>135383280</v>
       </c>
       <c r="B51" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>135383276</v>
       </c>
       <c r="B52" t="n">
-        <v>93307</v>
+        <v>93334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>135374074</v>
       </c>
       <c r="B53" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>135383278</v>
       </c>
       <c r="B54" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>135383279</v>
       </c>
       <c r="B55" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>135382693</v>
       </c>
       <c r="B56" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>135380357</v>
       </c>
       <c r="B58" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>135380644</v>
       </c>
       <c r="B59" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135380651</v>
       </c>
       <c r="B60" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>135383012</v>
       </c>
       <c r="B61" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>135380648</v>
       </c>
       <c r="B63" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135384615</v>
       </c>
       <c r="B64" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>135380361</v>
       </c>
       <c r="B65" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135380645</v>
       </c>
       <c r="B66" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>135384617</v>
       </c>
       <c r="B67" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135380646</v>
       </c>
       <c r="B68" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>135383291</v>
       </c>
       <c r="B69" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>135380358</v>
       </c>
       <c r="B70" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>135383013</v>
       </c>
       <c r="B71" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135372813</v>
       </c>
       <c r="B72" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135372935</v>
       </c>
       <c r="B73" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>135372979</v>
       </c>
       <c r="B74" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>135380653</v>
       </c>
       <c r="B75" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>135383267</v>
       </c>
       <c r="B76" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135383268</v>
       </c>
       <c r="B77" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>135383272</v>
       </c>
       <c r="B78" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>135383275</v>
       </c>
       <c r="B79" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>135380652</v>
       </c>
       <c r="B80" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>135371985</v>
       </c>
       <c r="B81" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>135372847</v>
       </c>
       <c r="B82" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>135380650</v>
       </c>
       <c r="B83" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>135380654</v>
       </c>
       <c r="B84" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>135383010</v>
       </c>
       <c r="B85" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>135383011</v>
       </c>
       <c r="B86" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>135383014</v>
       </c>
       <c r="B87" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135383017</v>
       </c>
       <c r="B88" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135380360</v>
       </c>
       <c r="B89" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>135383284</v>
       </c>
       <c r="B90" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135383285</v>
       </c>
       <c r="B91" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>135380647</v>
       </c>
       <c r="B92" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>135382692</v>
       </c>
       <c r="B93" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135383288</v>
       </c>
       <c r="B94" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>135383273</v>
       </c>
       <c r="B95" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135383287</v>
       </c>
       <c r="B96" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>135380656</v>
       </c>
       <c r="B104" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>135383289</v>
       </c>
       <c r="B105" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>135383286</v>
       </c>
       <c r="B106" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>135373563</v>
       </c>
       <c r="B107" t="n">
-        <v>79088</v>
+        <v>79115</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>135372100</v>
       </c>
       <c r="B108" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>135372226</v>
       </c>
       <c r="B109" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>135373694</v>
       </c>
       <c r="B110" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>135380359</v>
       </c>
       <c r="B111" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>135380362</v>
       </c>
       <c r="B112" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>135380649</v>
       </c>
       <c r="B113" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>135383015</v>
       </c>
       <c r="B114" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>135383274</v>
       </c>
       <c r="B115" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>135380395</v>
       </c>
       <c r="B116" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>135380387</v>
       </c>
       <c r="B117" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>135380673</v>
       </c>
       <c r="B118" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>135383029</v>
       </c>
       <c r="B119" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>135380675</v>
       </c>
       <c r="B120" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>135380355</v>
       </c>
       <c r="B122" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>135380672</v>
       </c>
       <c r="B123" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>135380677</v>
       </c>
       <c r="B124" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135384635</v>
       </c>
       <c r="B125" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>135384640</v>
       </c>
       <c r="B126" t="n">
-        <v>92601</v>
+        <v>92628</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>135384636</v>
       </c>
       <c r="B127" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>135380391</v>
       </c>
       <c r="B128" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135384633</v>
       </c>
       <c r="B129" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>135380393</v>
       </c>
       <c r="B130" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>135380384</v>
       </c>
       <c r="B131" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>135383030</v>
       </c>
       <c r="B132" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>135383264</v>
       </c>
       <c r="B133" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>135380634</v>
       </c>
       <c r="B134" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135383031</v>
       </c>
       <c r="B135" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>135380383</v>
       </c>
       <c r="B136" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>135380385</v>
       </c>
       <c r="B137" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>135380386</v>
       </c>
       <c r="B138" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>135380636</v>
       </c>
       <c r="B139" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>135380643</v>
       </c>
       <c r="B140" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>135380354</v>
       </c>
       <c r="B141" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>135383262</v>
       </c>
       <c r="B142" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>135380397</v>
       </c>
       <c r="B143" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135380670</v>
       </c>
       <c r="B146" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>135383263</v>
       </c>
       <c r="B147" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>135384637</v>
       </c>
       <c r="B148" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>135380674</v>
       </c>
       <c r="B149" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>135380676</v>
       </c>
       <c r="B150" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>135380635</v>
       </c>
       <c r="B151" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>135371686</v>
       </c>
       <c r="B152" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>135380388</v>
       </c>
       <c r="B153" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>135380398</v>
       </c>
       <c r="B154" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>135380633</v>
       </c>
       <c r="B155" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>135380678</v>
       </c>
       <c r="B156" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>135383265</v>
       </c>
       <c r="B157" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>135380680</v>
       </c>
       <c r="B161" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>135380351</v>
       </c>
       <c r="B162" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>135380352</v>
       </c>
       <c r="B163" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>135380402</v>
       </c>
       <c r="B164" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>135380625</v>
       </c>
       <c r="B165" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>135380631</v>
       </c>
       <c r="B166" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>135380638</v>
       </c>
       <c r="B167" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>135380639</v>
       </c>
       <c r="B168" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>135380353</v>
       </c>
       <c r="B169" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>135380403</v>
       </c>
       <c r="B170" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>135380679</v>
       </c>
       <c r="B171" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>135380627</v>
       </c>
       <c r="B172" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>135380641</v>
       </c>
       <c r="B173" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>135383032</v>
       </c>
       <c r="B174" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>135380401</v>
       </c>
       <c r="B175" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>135380637</v>
       </c>
       <c r="B178" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>135383292</v>
       </c>
       <c r="B179" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>135380682</v>
       </c>
       <c r="B180" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>135380400</v>
       </c>
       <c r="B181" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>135380626</v>
       </c>
       <c r="B182" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>135382212</v>
       </c>
       <c r="B184" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>135382961</v>
       </c>
       <c r="B185" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>135382962</v>
       </c>
       <c r="B188" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>135382963</v>
       </c>
       <c r="B189" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>135380624</v>
       </c>
       <c r="B190" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>135380623</v>
       </c>
       <c r="B191" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>135380622</v>
       </c>
       <c r="B192" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>135383294</v>
       </c>
       <c r="B197" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>135380404</v>
       </c>
       <c r="B198" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>135383134</v>
       </c>
       <c r="B199" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>135383113</v>
       </c>
       <c r="B200" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>135383111</v>
       </c>
       <c r="B201" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>135383112</v>
       </c>
       <c r="B202" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>135383114</v>
       </c>
       <c r="B203" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>135383133</v>
       </c>
       <c r="B204" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>135383137</v>
       </c>
       <c r="B205" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>135382100</v>
       </c>
       <c r="B206" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>135382101</v>
       </c>
       <c r="B207" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>135382194</v>
       </c>
       <c r="B208" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>135383136</v>
       </c>
       <c r="B209" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>135382197</v>
       </c>
       <c r="B213" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>135382949</v>
       </c>
       <c r="B214" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>135382948</v>
       </c>
       <c r="B215" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>135383110</v>
       </c>
       <c r="B216" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>135383117</v>
       </c>
       <c r="B217" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>135383119</v>
       </c>
       <c r="B218" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>135377466</v>
       </c>
       <c r="B219" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>135382206</v>
       </c>
       <c r="B220" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>135377473</v>
       </c>
       <c r="B221" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>135377376</v>
       </c>
       <c r="B222" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>135377387</v>
       </c>
       <c r="B223" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>135377497</v>
       </c>
       <c r="B224" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>135379379</v>
       </c>
       <c r="B225" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>135379385</v>
       </c>
       <c r="B226" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>135382208</v>
       </c>
       <c r="B227" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>135383692</v>
       </c>
       <c r="B228" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>135377396</v>
       </c>
       <c r="B229" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>135377400</v>
       </c>
       <c r="B230" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>135377468</v>
       </c>
       <c r="B231" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>135379373</v>
       </c>
       <c r="B232" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>135379374</v>
       </c>
       <c r="B233" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>135379376</v>
       </c>
       <c r="B234" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>135383138</v>
       </c>
       <c r="B235" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>135377481</v>
       </c>
       <c r="B236" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>135382207</v>
       </c>
       <c r="B237" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>135377467</v>
       </c>
       <c r="B238" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>135377494</v>
       </c>
       <c r="B239" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>135547424</v>
       </c>
       <c r="B240" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>135379387</v>
       </c>
       <c r="B241" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>135377485</v>
       </c>
       <c r="B242" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>135377107</v>
       </c>
       <c r="B243" t="n">
-        <v>87665</v>
+        <v>87692</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>135382303</v>
       </c>
       <c r="B244" t="n">
-        <v>87665</v>
+        <v>87692</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>135377083</v>
       </c>
       <c r="B245" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>135377084</v>
       </c>
       <c r="B246" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>135377086</v>
       </c>
       <c r="B247" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>135377102</v>
       </c>
       <c r="B248" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>135377109</v>
       </c>
       <c r="B249" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>135377371</v>
       </c>
       <c r="B250" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>135377378</v>
       </c>
       <c r="B251" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>135377388</v>
       </c>
       <c r="B252" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>135377391</v>
       </c>
       <c r="B253" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>135377392</v>
       </c>
       <c r="B254" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>135377460</v>
       </c>
       <c r="B255" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>135377461</v>
       </c>
       <c r="B256" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>135377465</v>
       </c>
       <c r="B257" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>135377477</v>
       </c>
       <c r="B258" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>135377482</v>
       </c>
       <c r="B259" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>135377483</v>
       </c>
       <c r="B260" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>135377487</v>
       </c>
       <c r="B261" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>135377489</v>
       </c>
       <c r="B262" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>135379369</v>
       </c>
       <c r="B263" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>135379386</v>
       </c>
       <c r="B264" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>135382209</v>
       </c>
       <c r="B265" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>135382302</v>
       </c>
       <c r="B266" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>135382957</v>
       </c>
       <c r="B267" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>135383689</v>
       </c>
       <c r="B268" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>135377369</v>
       </c>
       <c r="B269" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>135377383</v>
       </c>
       <c r="B270" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>135377384</v>
       </c>
       <c r="B271" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>135377395</v>
       </c>
       <c r="B272" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>135382200</v>
       </c>
       <c r="B273" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>135382952</v>
       </c>
       <c r="B274" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>135377393</v>
       </c>
       <c r="B275" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>135377479</v>
       </c>
       <c r="B276" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>135382202</v>
       </c>
       <c r="B277" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>135383141</v>
       </c>
       <c r="B278" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>135377087</v>
       </c>
       <c r="B279" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>135377370</v>
       </c>
       <c r="B280" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>135377375</v>
       </c>
       <c r="B281" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>135377394</v>
       </c>
       <c r="B282" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>135377398</v>
       </c>
       <c r="B283" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>135377492</v>
       </c>
       <c r="B284" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>135379381</v>
       </c>
       <c r="B285" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>135379382</v>
       </c>
       <c r="B286" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>135379388</v>
       </c>
       <c r="B287" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>135383691</v>
       </c>
       <c r="B288" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>135383697</v>
       </c>
       <c r="B289" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>135377091</v>
       </c>
       <c r="B290" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>135377475</v>
       </c>
       <c r="B291" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>135377476</v>
       </c>
       <c r="B292" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>135382298</v>
       </c>
       <c r="B293" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>135383139</v>
       </c>
       <c r="B294" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>135383140</v>
       </c>
       <c r="B295" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>135382097</v>
       </c>
       <c r="B296" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>135377379</v>
       </c>
       <c r="B297" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>135382201</v>
       </c>
       <c r="B298" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>135382954</v>
       </c>
       <c r="B303" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>135383687</v>
       </c>
       <c r="B304" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>135379371</v>
       </c>
       <c r="B305" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>135377085</v>
       </c>
       <c r="B306" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>135377110</v>
       </c>
       <c r="B307" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>135377111</v>
       </c>
       <c r="B308" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>135377112</v>
       </c>
       <c r="B309" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>135377114</v>
       </c>
       <c r="B310" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>135377478</v>
       </c>
       <c r="B311" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>135377488</v>
       </c>
       <c r="B312" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>135382937</v>
       </c>
       <c r="B313" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>135382956</v>
       </c>
       <c r="B314" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135382959</v>
       </c>
       <c r="B315" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>135377092</v>
       </c>
       <c r="B316" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135377093</v>
       </c>
       <c r="B317" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135377094</v>
       </c>
       <c r="B318" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>135377095</v>
       </c>
       <c r="B319" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>135377097</v>
       </c>
       <c r="B320" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>135377098</v>
       </c>
       <c r="B321" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>135377100</v>
       </c>
       <c r="B322" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>135377108</v>
       </c>
       <c r="B323" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>135377471</v>
       </c>
       <c r="B324" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>135377472</v>
       </c>
       <c r="B325" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>135377480</v>
       </c>
       <c r="B326" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>135382090</v>
       </c>
       <c r="B327" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>135382094</v>
       </c>
       <c r="B328" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>135382299</v>
       </c>
       <c r="B329" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>135382300</v>
       </c>
       <c r="B330" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>135382939</v>
       </c>
       <c r="B331" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>135382940</v>
       </c>
       <c r="B332" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>135382941</v>
       </c>
       <c r="B333" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>135382944</v>
       </c>
       <c r="B334" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>135382946</v>
       </c>
       <c r="B335" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>135382947</v>
       </c>
       <c r="B336" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>135382960</v>
       </c>
       <c r="B337" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>135385107</v>
       </c>
       <c r="B338" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>135377089</v>
       </c>
       <c r="B339" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>135377463</v>
       </c>
       <c r="B340" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>135379370</v>
       </c>
       <c r="B341" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>135377096</v>
       </c>
       <c r="B342" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>135377464</v>
       </c>
       <c r="B343" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>135382096</v>
       </c>
       <c r="B344" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>135382945</v>
       </c>
       <c r="B345" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>135379378</v>
       </c>
       <c r="B346" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>135377104</v>
       </c>
       <c r="B347" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>135377374</v>
       </c>
       <c r="B348" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>135377389</v>
       </c>
       <c r="B349" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>135377484</v>
       </c>
       <c r="B350" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>135379372</v>
       </c>
       <c r="B351" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>135379380</v>
       </c>
       <c r="B352" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>135379383</v>
       </c>
       <c r="B353" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>135382089</v>
       </c>
       <c r="B354" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>135382095</v>
       </c>
       <c r="B355" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>135382099</v>
       </c>
       <c r="B356" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>135382205</v>
       </c>
       <c r="B357" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>135382938</v>
       </c>
       <c r="B358" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>135382942</v>
       </c>
       <c r="B359" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>135382953</v>
       </c>
       <c r="B360" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>135383686</v>
       </c>
       <c r="B361" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>135383693</v>
       </c>
       <c r="B362" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>135383695</v>
       </c>
       <c r="B363" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>135383690</v>
       </c>
       <c r="B364" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>135377090</v>
       </c>
       <c r="B365" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>135377462</v>
       </c>
       <c r="B366" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>135379384</v>
       </c>
       <c r="B367" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>135377372</v>
       </c>
       <c r="B368" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>135377490</v>
       </c>
       <c r="B369" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>135377399</v>
       </c>
       <c r="B370" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>135377407</v>
       </c>
       <c r="B371" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>135377411</v>
       </c>
       <c r="B372" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>135377425</v>
       </c>
       <c r="B373" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>135377402</v>
       </c>
       <c r="B374" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>135377499</v>
       </c>
       <c r="B378" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>135383144</v>
       </c>
       <c r="B379" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>135383147</v>
       </c>
       <c r="B380" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>135383149</v>
       </c>
       <c r="B381" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>135377136</v>
       </c>
       <c r="B382" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>135377422</v>
       </c>
       <c r="B383" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>135377403</v>
       </c>
       <c r="B384" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>135377415</v>
       </c>
       <c r="B385" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>135377423</v>
       </c>
       <c r="B386" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>135377501</v>
       </c>
       <c r="B387" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>135377506</v>
       </c>
       <c r="B388" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>135379363</v>
       </c>
       <c r="B389" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>135379394</v>
       </c>
       <c r="B390" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>135379399</v>
       </c>
       <c r="B391" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>135382965</v>
       </c>
       <c r="B392" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>135383152</v>
       </c>
       <c r="B393" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>135377408</v>
       </c>
       <c r="B394" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>135377420</v>
       </c>
       <c r="B395" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>135379390</v>
       </c>
       <c r="B396" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>135379393</v>
       </c>
       <c r="B397" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>135379395</v>
       </c>
       <c r="B398" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>135379398</v>
       </c>
       <c r="B399" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>135383146</v>
       </c>
       <c r="B400" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>135377125</v>
       </c>
       <c r="B401" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>135377508</v>
       </c>
       <c r="B402" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>135377509</v>
       </c>
       <c r="B403" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>135377518</v>
       </c>
       <c r="B404" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>135377519</v>
       </c>
       <c r="B405" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>135377512</v>
       </c>
       <c r="B406" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>135379397</v>
       </c>
       <c r="B407" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>135377510</v>
       </c>
       <c r="B408" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>135377513</v>
       </c>
       <c r="B409" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>135377517</v>
       </c>
       <c r="B410" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>135377520</v>
       </c>
       <c r="B411" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>135377511</v>
       </c>
       <c r="B412" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>135377521</v>
       </c>
       <c r="B413" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>135379401</v>
       </c>
       <c r="B414" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>135377404</v>
       </c>
       <c r="B415" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>135377140</v>
       </c>
       <c r="B421" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>135379389</v>
       </c>
       <c r="B422" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>135383143</v>
       </c>
       <c r="B423" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>135383145</v>
       </c>
       <c r="B424" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>135383151</v>
       </c>
       <c r="B425" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>135377126</v>
       </c>
       <c r="B426" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>135382964</v>
       </c>
       <c r="B427" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>135377401</v>
       </c>
       <c r="B428" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>135379396</v>
       </c>
       <c r="B429" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>135383150</v>
       </c>
       <c r="B430" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>135377405</v>
       </c>
       <c r="B431" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>135377416</v>
       </c>
       <c r="B432" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>135377502</v>
       </c>
       <c r="B433" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>135377505</v>
       </c>
       <c r="B434" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>135377118</v>
       </c>
       <c r="B435" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>135377119</v>
       </c>
       <c r="B436" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>135377121</v>
       </c>
       <c r="B437" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>135377130</v>
       </c>
       <c r="B438" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>135377137</v>
       </c>
       <c r="B439" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>135377138</v>
       </c>
       <c r="B440" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>135377139</v>
       </c>
       <c r="B441" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>135377144</v>
       </c>
       <c r="B442" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>135377410</v>
       </c>
       <c r="B443" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>135377414</v>
       </c>
       <c r="B444" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>135377503</v>
       </c>
       <c r="B445" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>135379365</v>
       </c>
       <c r="B446" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>135379400</v>
       </c>
       <c r="B447" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>135382967</v>
       </c>
       <c r="B448" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>135382968</v>
       </c>
       <c r="B449" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>135383698</v>
       </c>
       <c r="B450" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>135377413</v>
       </c>
       <c r="B451" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>135377419</v>
       </c>
       <c r="B452" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>135377500</v>
       </c>
       <c r="B453" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>135377514</v>
       </c>
       <c r="B454" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>135377145</v>
       </c>
       <c r="B455" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>135383123</v>
       </c>
       <c r="B456" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>135383120</v>
       </c>
       <c r="B457" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>135383129</v>
       </c>
       <c r="B458" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>135383125</v>
       </c>
       <c r="B459" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>135383126</v>
       </c>
       <c r="B460" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -53893,7 +53893,7 @@
         <v>135383128</v>
       </c>
       <c r="B461" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>135383122</v>
       </c>
       <c r="B462" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>135382092</v>
       </c>
       <c r="B463" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54241,7 +54241,7 @@
         <v>135383107</v>
       </c>
       <c r="B464" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>135383124</v>
       </c>
       <c r="B465" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>135382093</v>
       </c>
       <c r="B466" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>135383130</v>
       </c>
       <c r="B467" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>135383121</v>
       </c>
       <c r="B468" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>135383127</v>
       </c>
       <c r="B469" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>135383132</v>
       </c>
       <c r="B470" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>135382296</v>
       </c>
       <c r="B471" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>135377080</v>
       </c>
       <c r="B472" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>135377081</v>
       </c>
       <c r="B473" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>135379368</v>
       </c>
       <c r="B474" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>135382936</v>
       </c>
       <c r="B475" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>135377079</v>
       </c>
       <c r="B476" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>135377442</v>
       </c>
       <c r="B477" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>135377532</v>
       </c>
       <c r="B478" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>135379350</v>
       </c>
       <c r="B479" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>135383684</v>
       </c>
       <c r="B480" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>135377523</v>
       </c>
       <c r="B481" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>135377522</v>
       </c>
       <c r="B482" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>135377347</v>
       </c>
       <c r="B483" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>135377350</v>
       </c>
       <c r="B484" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>135379355</v>
       </c>
       <c r="B485" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>135377070</v>
       </c>
       <c r="B486" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>135377525</v>
       </c>
       <c r="B487" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>135379356</v>
       </c>
       <c r="B488" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>135379358</v>
       </c>
       <c r="B489" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>135379360</v>
       </c>
       <c r="B490" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>135377074</v>
       </c>
       <c r="B491" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -57484,7 +57484,7 @@
         <v>135377348</v>
       </c>
       <c r="B492" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -57600,7 +57600,7 @@
         <v>135377351</v>
       </c>
       <c r="B493" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>135377368</v>
       </c>
       <c r="B494" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>135377439</v>
       </c>
       <c r="B495" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>135377448</v>
       </c>
       <c r="B496" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>135377529</v>
       </c>
       <c r="B497" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58180,7 +58180,7 @@
         <v>135377530</v>
       </c>
       <c r="B498" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>135377533</v>
       </c>
       <c r="B499" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>135379351</v>
       </c>
       <c r="B500" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -58528,7 +58528,7 @@
         <v>135383685</v>
       </c>
       <c r="B501" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>135377363</v>
       </c>
       <c r="B502" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>135377367</v>
       </c>
       <c r="B503" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -58866,7 +58866,7 @@
         <v>135377441</v>
       </c>
       <c r="B504" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         <v>135377444</v>
       </c>
       <c r="B505" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>135379352</v>
       </c>
       <c r="B506" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>135379354</v>
       </c>
       <c r="B507" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>135382294</v>
       </c>
       <c r="B508" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>135382295</v>
       </c>
       <c r="B509" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>135377455</v>
       </c>
       <c r="B510" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59683,7 +59683,7 @@
         <v>135377361</v>
       </c>
       <c r="B511" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>135377071</v>
       </c>
       <c r="B512" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>135377353</v>
       </c>
       <c r="B513" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>135377527</v>
       </c>
       <c r="B514" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>135379359</v>
       </c>
       <c r="B515" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>135379361</v>
       </c>
       <c r="B516" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>135377447</v>
       </c>
       <c r="B517" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>135377526</v>
       </c>
       <c r="B518" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>135377355</v>
       </c>
       <c r="B521" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>135377451</v>
       </c>
       <c r="B522" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>135383683</v>
       </c>
       <c r="B523" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>135377354</v>
       </c>
       <c r="B524" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>135377453</v>
       </c>
       <c r="B525" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>135377360</v>
       </c>
       <c r="B526" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>135377458</v>
       </c>
       <c r="B527" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>135377524</v>
       </c>
       <c r="B528" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -61766,7 +61766,7 @@
         <v>135377364</v>
       </c>
       <c r="B529" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -61882,7 +61882,7 @@
         <v>135377436</v>
       </c>
       <c r="B530" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>135377449</v>
       </c>
       <c r="B531" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>135377076</v>
       </c>
       <c r="B532" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>135377077</v>
       </c>
       <c r="B533" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>135377440</v>
       </c>
       <c r="B534" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62466,7 +62466,7 @@
         <v>135379353</v>
       </c>
       <c r="B535" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -62582,7 +62582,7 @@
         <v>135377446</v>
       </c>
       <c r="B536" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -26544,7 +26544,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -30971,7 +30971,7 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
@@ -47272,7 +47272,7 @@
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
@@ -47388,7 +47388,7 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
@@ -47504,7 +47504,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -48316,7 +48316,7 @@
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
@@ -53067,7 +53067,7 @@
       </c>
       <c r="AX453" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY453" t="inlineStr">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="AX482" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY482" t="inlineStr">
@@ -58161,7 +58161,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="AX498" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY498" t="inlineStr">
@@ -60128,7 +60128,7 @@
       </c>
       <c r="AX514" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY514" t="inlineStr">
@@ -60592,7 +60592,7 @@
       </c>
       <c r="AX518" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY518" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -26544,7 +26544,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -30971,7 +30971,7 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
@@ -47272,7 +47272,7 @@
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
@@ -47388,7 +47388,7 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
@@ -47504,7 +47504,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -48316,7 +48316,7 @@
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
@@ -53067,7 +53067,7 @@
       </c>
       <c r="AX453" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY453" t="inlineStr">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="AX482" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY482" t="inlineStr">
@@ -58161,7 +58161,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="AX498" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY498" t="inlineStr">
@@ -60128,7 +60128,7 @@
       </c>
       <c r="AX514" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY514" t="inlineStr">
@@ -60592,7 +60592,7 @@
       </c>
       <c r="AX518" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY518" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135380374</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135387752</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135384620</v>
       </c>
       <c r="B8" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>135384621</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135384624</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135380660</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135380363</v>
       </c>
       <c r="B12" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135380367</v>
       </c>
       <c r="B13" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>135380368</v>
       </c>
       <c r="B14" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135380375</v>
       </c>
       <c r="B15" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135380664</v>
       </c>
       <c r="B16" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135384623</v>
       </c>
       <c r="B17" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135380657</v>
       </c>
       <c r="B18" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135380658</v>
       </c>
       <c r="B19" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>135380377</v>
       </c>
       <c r="B41" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>135380380</v>
       </c>
       <c r="B42" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>135383280</v>
       </c>
       <c r="B51" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>135383276</v>
       </c>
       <c r="B52" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>135374074</v>
       </c>
       <c r="B53" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>135382693</v>
       </c>
       <c r="B56" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135384615</v>
       </c>
       <c r="B64" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>135380361</v>
       </c>
       <c r="B65" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135380645</v>
       </c>
       <c r="B66" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>135384617</v>
       </c>
       <c r="B67" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135380646</v>
       </c>
       <c r="B68" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>135383291</v>
       </c>
       <c r="B69" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>135380358</v>
       </c>
       <c r="B70" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>135383013</v>
       </c>
       <c r="B71" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135372813</v>
       </c>
       <c r="B72" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135372935</v>
       </c>
       <c r="B73" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>135372979</v>
       </c>
       <c r="B74" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>135380653</v>
       </c>
       <c r="B75" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>135383267</v>
       </c>
       <c r="B76" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135383268</v>
       </c>
       <c r="B77" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>135383272</v>
       </c>
       <c r="B78" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>135383275</v>
       </c>
       <c r="B79" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>135380652</v>
       </c>
       <c r="B80" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>135380656</v>
       </c>
       <c r="B104" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>135383289</v>
       </c>
       <c r="B105" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>135383286</v>
       </c>
       <c r="B106" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>135380395</v>
       </c>
       <c r="B116" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>135380387</v>
       </c>
       <c r="B117" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>135380673</v>
       </c>
       <c r="B118" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>135383029</v>
       </c>
       <c r="B119" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>135384640</v>
       </c>
       <c r="B126" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>135384636</v>
       </c>
       <c r="B127" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135384633</v>
       </c>
       <c r="B129" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>135380393</v>
       </c>
       <c r="B130" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>135380384</v>
       </c>
       <c r="B131" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>135383030</v>
       </c>
       <c r="B132" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>135383264</v>
       </c>
       <c r="B133" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135380670</v>
       </c>
       <c r="B146" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>135383263</v>
       </c>
       <c r="B147" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>135384637</v>
       </c>
       <c r="B148" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>135380674</v>
       </c>
       <c r="B149" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>135380676</v>
       </c>
       <c r="B150" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>135380680</v>
       </c>
       <c r="B161" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>135380638</v>
       </c>
       <c r="B167" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>135380639</v>
       </c>
       <c r="B168" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>135380353</v>
       </c>
       <c r="B169" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>135380403</v>
       </c>
       <c r="B170" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>135380679</v>
       </c>
       <c r="B171" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>135380637</v>
       </c>
       <c r="B178" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>135383292</v>
       </c>
       <c r="B179" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>135380682</v>
       </c>
       <c r="B180" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>135382212</v>
       </c>
       <c r="B184" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>135382961</v>
       </c>
       <c r="B185" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>135383134</v>
       </c>
       <c r="B199" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>135383113</v>
       </c>
       <c r="B200" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>135382197</v>
       </c>
       <c r="B213" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>135382949</v>
       </c>
       <c r="B214" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>135382948</v>
       </c>
       <c r="B215" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>135377466</v>
       </c>
       <c r="B219" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>135382206</v>
       </c>
       <c r="B220" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>135379385</v>
       </c>
       <c r="B226" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>135382208</v>
       </c>
       <c r="B227" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>135377468</v>
       </c>
       <c r="B231" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>135379373</v>
       </c>
       <c r="B232" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>135379374</v>
       </c>
       <c r="B233" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>135379376</v>
       </c>
       <c r="B234" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>135383138</v>
       </c>
       <c r="B235" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>135377481</v>
       </c>
       <c r="B236" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>135382207</v>
       </c>
       <c r="B237" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>135377467</v>
       </c>
       <c r="B238" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>135377494</v>
       </c>
       <c r="B239" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>135547424</v>
       </c>
       <c r="B240" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>135379387</v>
       </c>
       <c r="B241" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>135377485</v>
       </c>
       <c r="B242" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>135377107</v>
       </c>
       <c r="B243" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>135382303</v>
       </c>
       <c r="B244" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>135382954</v>
       </c>
       <c r="B303" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>135383687</v>
       </c>
       <c r="B304" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>135379371</v>
       </c>
       <c r="B305" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>135377085</v>
       </c>
       <c r="B306" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>135377110</v>
       </c>
       <c r="B307" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>135377111</v>
       </c>
       <c r="B308" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>135377112</v>
       </c>
       <c r="B309" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>135377114</v>
       </c>
       <c r="B310" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>135377478</v>
       </c>
       <c r="B311" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>135377488</v>
       </c>
       <c r="B312" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>135382937</v>
       </c>
       <c r="B313" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>135382956</v>
       </c>
       <c r="B314" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135382959</v>
       </c>
       <c r="B315" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>135377092</v>
       </c>
       <c r="B316" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135377093</v>
       </c>
       <c r="B317" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135377094</v>
       </c>
       <c r="B318" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>135377095</v>
       </c>
       <c r="B319" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>135377097</v>
       </c>
       <c r="B320" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>135377098</v>
       </c>
       <c r="B321" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>135377100</v>
       </c>
       <c r="B322" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>135377108</v>
       </c>
       <c r="B323" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>135377471</v>
       </c>
       <c r="B324" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>135377472</v>
       </c>
       <c r="B325" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>135377480</v>
       </c>
       <c r="B326" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>135382090</v>
       </c>
       <c r="B327" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>135382094</v>
       </c>
       <c r="B328" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>135382299</v>
       </c>
       <c r="B329" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>135382300</v>
       </c>
       <c r="B330" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>135382939</v>
       </c>
       <c r="B331" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>135382940</v>
       </c>
       <c r="B332" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>135382941</v>
       </c>
       <c r="B333" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>135382944</v>
       </c>
       <c r="B334" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>135382946</v>
       </c>
       <c r="B335" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>135382947</v>
       </c>
       <c r="B336" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>135382960</v>
       </c>
       <c r="B337" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>135385107</v>
       </c>
       <c r="B338" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>135377089</v>
       </c>
       <c r="B339" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>135377463</v>
       </c>
       <c r="B340" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>135379370</v>
       </c>
       <c r="B341" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>135377096</v>
       </c>
       <c r="B342" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>135377464</v>
       </c>
       <c r="B343" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>135382096</v>
       </c>
       <c r="B344" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>135382945</v>
       </c>
       <c r="B345" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>135379378</v>
       </c>
       <c r="B346" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>135377104</v>
       </c>
       <c r="B347" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>135377374</v>
       </c>
       <c r="B348" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>135377389</v>
       </c>
       <c r="B349" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>135377484</v>
       </c>
       <c r="B350" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>135379372</v>
       </c>
       <c r="B351" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>135379380</v>
       </c>
       <c r="B352" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>135379383</v>
       </c>
       <c r="B353" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>135382089</v>
       </c>
       <c r="B354" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>135382095</v>
       </c>
       <c r="B355" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>135382099</v>
       </c>
       <c r="B356" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>135382205</v>
       </c>
       <c r="B357" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>135382938</v>
       </c>
       <c r="B358" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>135382942</v>
       </c>
       <c r="B359" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>135382953</v>
       </c>
       <c r="B360" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>135383686</v>
       </c>
       <c r="B361" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>135383693</v>
       </c>
       <c r="B362" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>135383695</v>
       </c>
       <c r="B363" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>135383690</v>
       </c>
       <c r="B364" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>135377090</v>
       </c>
       <c r="B365" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>135377462</v>
       </c>
       <c r="B366" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>135377499</v>
       </c>
       <c r="B378" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>135383144</v>
       </c>
       <c r="B379" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>135383147</v>
       </c>
       <c r="B380" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>135383149</v>
       </c>
       <c r="B381" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>135377140</v>
       </c>
       <c r="B421" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>135379389</v>
       </c>
       <c r="B422" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>135383143</v>
       </c>
       <c r="B423" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>135383145</v>
       </c>
       <c r="B424" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>135383151</v>
       </c>
       <c r="B425" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>135377126</v>
       </c>
       <c r="B426" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>135382964</v>
       </c>
       <c r="B427" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>135383129</v>
       </c>
       <c r="B458" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>135383125</v>
       </c>
       <c r="B459" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>135382093</v>
       </c>
       <c r="B466" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>135383130</v>
       </c>
       <c r="B467" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>135382296</v>
       </c>
       <c r="B471" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>135382936</v>
       </c>
       <c r="B475" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>135377523</v>
       </c>
       <c r="B481" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>135377522</v>
       </c>
       <c r="B482" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>135377355</v>
       </c>
       <c r="B521" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>135377451</v>
       </c>
       <c r="B522" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>135383683</v>
       </c>
       <c r="B523" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>135377354</v>
       </c>
       <c r="B524" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>135377453</v>
       </c>
       <c r="B525" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>135377360</v>
       </c>
       <c r="B526" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62714,6 +62714,9 @@
         </is>
       </c>
       <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr"/>
+      <c r="N537" t="inlineStr"/>
       <c r="P537" t="inlineStr">
         <is>
           <t>Råssnenjárrga, Pi lm</t>
@@ -62779,8 +62782,14 @@
       <c r="AE537" t="b">
         <v>0</v>
       </c>
+      <c r="AF537" t="inlineStr"/>
       <c r="AG537" t="b">
         <v>0</v>
+      </c>
+      <c r="AP537" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
       </c>
       <c r="AT537" t="inlineStr"/>
       <c r="AW537" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -27926,7 +27926,7 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -30159,7 +30159,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -38170,7 +38170,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -38286,7 +38286,7 @@
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -45416,7 +45416,7 @@
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
@@ -47620,7 +47620,7 @@
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
@@ -47968,7 +47968,7 @@
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr">
@@ -52164,7 +52164,7 @@
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
@@ -53178,7 +53178,7 @@
       </c>
       <c r="AX454" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY454" t="inlineStr">
@@ -56300,7 +56300,7 @@
       </c>
       <c r="AX481" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY481" t="inlineStr">
@@ -57001,7 +57001,7 @@
       </c>
       <c r="AX487" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY487" t="inlineStr">
@@ -57929,7 +57929,7 @@
       </c>
       <c r="AX495" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY495" t="inlineStr">
@@ -58393,7 +58393,7 @@
       </c>
       <c r="AX499" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY499" t="inlineStr">
@@ -61061,7 +61061,7 @@
       </c>
       <c r="AX522" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY522" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AX528" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY528" t="inlineStr">
@@ -62447,7 +62447,7 @@
       </c>
       <c r="AX534" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
+          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY534" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -27926,7 +27926,7 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -30159,7 +30159,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -38170,7 +38170,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -38286,7 +38286,7 @@
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -45416,7 +45416,7 @@
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
@@ -47620,7 +47620,7 @@
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
@@ -47968,7 +47968,7 @@
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr">
@@ -52164,7 +52164,7 @@
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
@@ -53178,7 +53178,7 @@
       </c>
       <c r="AX454" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY454" t="inlineStr">
@@ -56300,7 +56300,7 @@
       </c>
       <c r="AX481" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY481" t="inlineStr">
@@ -57001,7 +57001,7 @@
       </c>
       <c r="AX487" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY487" t="inlineStr">
@@ -57929,7 +57929,7 @@
       </c>
       <c r="AX495" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY495" t="inlineStr">
@@ -58393,7 +58393,7 @@
       </c>
       <c r="AX499" t="inlineStr">
         <is>
-          <t>Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY499" t="inlineStr">
@@ -61061,7 +61061,7 @@
       </c>
       <c r="AX522" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY522" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AX528" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY528" t="inlineStr">
@@ -62447,7 +62447,7 @@
       </c>
       <c r="AX534" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Sofia Fransén, Martin Axegård, Alva Danielsson, Tyr Nilsson, Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Moa Turid Lövdahl, Tyr Nilsson, Alva Danielsson, Martin Axegård, Sofia Fransén</t>
         </is>
       </c>
       <c r="AY534" t="inlineStr">

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -28294,7 +28294,7 @@
         <v>135547424</v>
       </c>
       <c r="B240" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -28294,7 +28294,7 @@
         <v>135547424</v>
       </c>
       <c r="B240" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80338</v>
+        <v>80339</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80339</v>
+        <v>80343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80343</v>
+        <v>80344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80344</v>
+        <v>80348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62693,7 +62693,7 @@
         <v>135377456</v>
       </c>
       <c r="B537" t="n">
-        <v>80348</v>
+        <v>80354</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -62925,7 +62925,7 @@
         <v>135377456</v>
       </c>
       <c r="B539" t="n">
-        <v>80354</v>
+        <v>80367</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>

--- a/artfynd/Iksjak-Råssnesudden artfynd.xlsx
+++ b/artfynd/Iksjak-Råssnesudden artfynd.xlsx
@@ -15326,7 +15326,7 @@
         <v>135380389</v>
       </c>
       <c r="B128" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135380390</v>
       </c>
       <c r="B129" t="n">
-        <v>83465</v>
+        <v>83466</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>135377456</v>
       </c>
       <c r="B539" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
